--- a/sum_daily_order/result/Weekly_Performance_Report_JP_local.xlsx
+++ b/sum_daily_order/result/Weekly_Performance_Report_JP_local.xlsx
@@ -10,13 +10,14 @@
     <sheet name="Weekly Summary" sheetId="1" r:id="rId1"/>
     <sheet name="Category Aggregation" sheetId="2" r:id="rId2"/>
     <sheet name="Product Quantity Detail" sheetId="3" r:id="rId3"/>
+    <sheet name="Sample Statistics" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="24">
   <si>
     <t>文件名称</t>
   </si>
@@ -42,10 +43,10 @@
     <t>寄样总支出(含物流)</t>
   </si>
   <si>
-    <t>全部 笔订单-2026-02-27-10_43.csv</t>
-  </si>
-  <si>
-    <t>2026-02-26</t>
+    <t>全部 笔订单-2026-02-28-18_41.csv</t>
+  </si>
+  <si>
+    <t>2026-02-28</t>
   </si>
   <si>
     <t>日期</t>
@@ -69,6 +70,9 @@
     <t>寄样支出</t>
   </si>
   <si>
+    <t>头发护理精华</t>
+  </si>
+  <si>
     <t>电动剃眉刀</t>
   </si>
   <si>
@@ -82,6 +86,9 @@
   </si>
   <si>
     <t>汇总</t>
+  </si>
+  <si>
+    <t>总样品数</t>
   </si>
 </sst>
 </file>
@@ -476,22 +483,22 @@
         <v>9</v>
       </c>
       <c r="C2">
-        <v>8673</v>
+        <v>31080</v>
       </c>
       <c r="D2">
-        <v>433.65</v>
+        <v>1554</v>
       </c>
       <c r="E2">
-        <v>7584</v>
+        <v>29090</v>
       </c>
       <c r="F2">
-        <v>53.2</v>
+        <v>183</v>
       </c>
       <c r="G2">
-        <v>167.5</v>
+        <v>557.5</v>
       </c>
       <c r="H2">
-        <v>53.4</v>
+        <v>927</v>
       </c>
     </row>
   </sheetData>
@@ -501,7 +508,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -538,22 +545,22 @@
         <v>17</v>
       </c>
       <c r="C2">
-        <v>1080</v>
+        <v>3528</v>
       </c>
       <c r="D2">
-        <v>594</v>
+        <v>3528</v>
       </c>
       <c r="E2">
-        <v>4.6</v>
+        <v>10</v>
       </c>
       <c r="F2">
-        <v>12.5</v>
+        <v>25</v>
       </c>
       <c r="G2">
-        <v>17.1</v>
+        <v>0</v>
       </c>
       <c r="H2">
-        <v>54</v>
+        <v>176.4</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -564,22 +571,22 @@
         <v>18</v>
       </c>
       <c r="C3">
-        <v>6695</v>
+        <v>6480</v>
       </c>
       <c r="D3">
-        <v>6092</v>
+        <v>5994</v>
       </c>
       <c r="E3">
-        <v>44</v>
+        <v>27.6</v>
       </c>
       <c r="F3">
-        <v>137.5</v>
+        <v>75</v>
       </c>
       <c r="G3">
-        <v>36.3</v>
+        <v>273.6</v>
       </c>
       <c r="H3">
-        <v>334.75</v>
+        <v>324</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -590,21 +597,47 @@
         <v>19</v>
       </c>
       <c r="C4">
+        <v>20174</v>
+      </c>
+      <c r="D4">
+        <v>18670</v>
+      </c>
+      <c r="E4">
+        <v>140.8</v>
+      </c>
+      <c r="F4">
+        <v>440</v>
+      </c>
+      <c r="G4">
+        <v>653.4</v>
+      </c>
+      <c r="H4">
+        <v>1008.7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C5">
         <v>898</v>
       </c>
-      <c r="D4">
+      <c r="D5">
         <v>898</v>
       </c>
-      <c r="E4">
+      <c r="E5">
         <v>4.6</v>
       </c>
-      <c r="F4">
+      <c r="F5">
         <v>17.5</v>
       </c>
-      <c r="G4">
+      <c r="G5">
         <v>0</v>
       </c>
-      <c r="H4">
+      <c r="H5">
         <v>44.9</v>
       </c>
     </row>
@@ -615,12 +648,12 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>9</v>
@@ -628,18 +661,18 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B2">
-        <v>5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B3">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -652,10 +685,83 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B6">
+        <v>24</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
         <v>21</v>
       </c>
+      <c r="B1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B2">
+        <v>18</v>
+      </c>
+      <c r="C2">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B3">
+        <v>16</v>
+      </c>
+      <c r="C3">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B4">
+        <v>6</v>
+      </c>
+      <c r="C4">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" s="1" t="s">
+        <v>22</v>
+      </c>
       <c r="B5">
-        <v>7</v>
+        <v>40</v>
+      </c>
+      <c r="C5">
+        <v>40</v>
       </c>
     </row>
   </sheetData>

--- a/sum_daily_order/result/Weekly_Performance_Report_JP_local.xlsx
+++ b/sum_daily_order/result/Weekly_Performance_Report_JP_local.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="26">
   <si>
     <t>文件名称</t>
   </si>
@@ -43,10 +43,16 @@
     <t>寄样总支出(含物流)</t>
   </si>
   <si>
-    <t>全部 笔订单-2026-02-28-18_41.csv</t>
-  </si>
-  <si>
-    <t>2026-02-28</t>
+    <t>0222.csv</t>
+  </si>
+  <si>
+    <t>0301.csv</t>
+  </si>
+  <si>
+    <t>2026-02-22</t>
+  </si>
+  <si>
+    <t>2026-03-01</t>
   </si>
   <si>
     <t>日期</t>
@@ -70,16 +76,16 @@
     <t>寄样支出</t>
   </si>
   <si>
+    <t>电动鼻毛刀</t>
+  </si>
+  <si>
+    <t>车载手机支架</t>
+  </si>
+  <si>
     <t>头发护理精华</t>
   </si>
   <si>
     <t>电动剃眉刀</t>
-  </si>
-  <si>
-    <t>电动鼻毛刀</t>
-  </si>
-  <si>
-    <t>车载手机支架</t>
   </si>
   <si>
     <t>商品名称</t>
@@ -446,7 +452,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -480,25 +486,51 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2">
+        <v>56246</v>
+      </c>
+      <c r="D2">
+        <v>2812.3</v>
+      </c>
+      <c r="E2">
+        <v>49138</v>
+      </c>
+      <c r="F2">
+        <v>399.2</v>
+      </c>
+      <c r="G2">
+        <v>735</v>
+      </c>
+      <c r="H2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" t="s">
         <v>9</v>
       </c>
-      <c r="C2">
-        <v>31080</v>
-      </c>
-      <c r="D2">
-        <v>1554</v>
-      </c>
-      <c r="E2">
-        <v>29090</v>
-      </c>
-      <c r="F2">
-        <v>183</v>
-      </c>
-      <c r="G2">
-        <v>557.5</v>
-      </c>
-      <c r="H2">
-        <v>927</v>
+      <c r="B3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3">
+        <v>72715</v>
+      </c>
+      <c r="D3">
+        <v>3635.75</v>
+      </c>
+      <c r="E3">
+        <v>66788</v>
+      </c>
+      <c r="F3">
+        <v>392.2</v>
+      </c>
+      <c r="G3">
+        <v>1033</v>
+      </c>
+      <c r="H3">
+        <v>972</v>
       </c>
     </row>
   </sheetData>
@@ -508,30 +540,30 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>3</v>
@@ -539,106 +571,158 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C2">
-        <v>3528</v>
+        <v>54450</v>
       </c>
       <c r="D2">
-        <v>3528</v>
+        <v>47342</v>
       </c>
       <c r="E2">
-        <v>10</v>
+        <v>390</v>
       </c>
       <c r="F2">
-        <v>25</v>
+        <v>700</v>
       </c>
       <c r="G2">
         <v>0</v>
       </c>
       <c r="H2">
-        <v>176.4</v>
+        <v>2722.5</v>
       </c>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C3">
-        <v>6480</v>
+        <v>1796</v>
       </c>
       <c r="D3">
-        <v>5994</v>
+        <v>1796</v>
       </c>
       <c r="E3">
-        <v>27.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="F3">
-        <v>75</v>
+        <v>35</v>
       </c>
       <c r="G3">
-        <v>273.6</v>
+        <v>0</v>
       </c>
       <c r="H3">
-        <v>324</v>
+        <v>89.8</v>
       </c>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C4">
-        <v>20174</v>
+        <v>27048</v>
       </c>
       <c r="D4">
-        <v>18670</v>
+        <v>24832</v>
       </c>
       <c r="E4">
-        <v>140.8</v>
+        <v>120</v>
       </c>
       <c r="F4">
-        <v>440</v>
+        <v>492</v>
       </c>
       <c r="G4">
-        <v>653.4</v>
+        <v>306</v>
       </c>
       <c r="H4">
-        <v>1008.7</v>
+        <v>1352.4</v>
       </c>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5">
+        <v>8640</v>
+      </c>
+      <c r="D5">
+        <v>8154</v>
+      </c>
+      <c r="E5">
+        <v>36.8</v>
+      </c>
+      <c r="F5">
+        <v>100</v>
+      </c>
+      <c r="G5">
+        <v>273.6</v>
+      </c>
+      <c r="H5">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" t="s">
+        <v>19</v>
+      </c>
+      <c r="C6">
+        <v>35231</v>
+      </c>
+      <c r="D6">
+        <v>32006</v>
+      </c>
+      <c r="E6">
+        <v>226.2</v>
+      </c>
+      <c r="F6">
+        <v>406</v>
+      </c>
+      <c r="G6">
+        <v>392.4</v>
+      </c>
+      <c r="H6">
+        <v>1761.55</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" t="s">
         <v>20</v>
       </c>
-      <c r="C5">
-        <v>898</v>
-      </c>
-      <c r="D5">
-        <v>898</v>
-      </c>
-      <c r="E5">
-        <v>4.6</v>
-      </c>
-      <c r="F5">
-        <v>17.5</v>
-      </c>
-      <c r="G5">
+      <c r="C7">
+        <v>1796</v>
+      </c>
+      <c r="D7">
+        <v>1796</v>
+      </c>
+      <c r="E7">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="F7">
+        <v>35</v>
+      </c>
+      <c r="G7">
         <v>0</v>
       </c>
-      <c r="H5">
-        <v>44.9</v>
+      <c r="H7">
+        <v>89.8</v>
       </c>
     </row>
   </sheetData>
@@ -648,55 +732,73 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2">
+        <v>10</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
       <c r="A2" s="1" t="s">
         <v>19</v>
       </c>
       <c r="B2">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2">
+        <v>50</v>
+      </c>
+      <c r="C2">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
       <c r="A3" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B3">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
       <c r="A4" s="1" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="B4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2">
+        <v>0</v>
+      </c>
+      <c r="C4">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
       <c r="A5" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2">
+        <v>0</v>
+      </c>
+      <c r="C5">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
       <c r="A6" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B6">
-        <v>24</v>
+        <v>52</v>
+      </c>
+      <c r="C6">
+        <v>51</v>
       </c>
     </row>
   </sheetData>
@@ -711,13 +813,13 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -733,7 +835,7 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="1" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="B3">
         <v>16</v>
@@ -744,7 +846,7 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="1" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="B4">
         <v>6</v>
@@ -755,7 +857,7 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B5">
         <v>40</v>

--- a/sum_daily_order/result/Weekly_Performance_Report_JP_local.xlsx
+++ b/sum_daily_order/result/Weekly_Performance_Report_JP_local.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="27">
   <si>
     <t>文件名称</t>
   </si>
@@ -43,16 +43,16 @@
     <t>寄样总支出(含物流)</t>
   </si>
   <si>
-    <t>0222.csv</t>
-  </si>
-  <si>
-    <t>0301.csv</t>
-  </si>
-  <si>
-    <t>2026-02-22</t>
-  </si>
-  <si>
-    <t>2026-03-01</t>
+    <t>0302.csv</t>
+  </si>
+  <si>
+    <t>0303.csv</t>
+  </si>
+  <si>
+    <t>2026-03-02</t>
+  </si>
+  <si>
+    <t>2026-03-03</t>
   </si>
   <si>
     <t>日期</t>
@@ -76,16 +76,19 @@
     <t>寄样支出</t>
   </si>
   <si>
+    <t>头发护理精华</t>
+  </si>
+  <si>
+    <t>电动剃眉刀</t>
+  </si>
+  <si>
     <t>电动鼻毛刀</t>
   </si>
   <si>
+    <t>白色睫毛推</t>
+  </si>
+  <si>
     <t>车载手机支架</t>
-  </si>
-  <si>
-    <t>头发护理精华</t>
-  </si>
-  <si>
-    <t>电动剃眉刀</t>
   </si>
   <si>
     <t>商品名称</t>
@@ -489,22 +492,22 @@
         <v>10</v>
       </c>
       <c r="C2">
-        <v>56246</v>
+        <v>16716</v>
       </c>
       <c r="D2">
-        <v>2812.3</v>
+        <v>835.8</v>
       </c>
       <c r="E2">
-        <v>49138</v>
+        <v>15679</v>
       </c>
       <c r="F2">
-        <v>399.2</v>
+        <v>88.3</v>
       </c>
       <c r="G2">
-        <v>735</v>
+        <v>297.95</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>578.4</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -515,22 +518,22 @@
         <v>11</v>
       </c>
       <c r="C3">
-        <v>72715</v>
+        <v>19208</v>
       </c>
       <c r="D3">
-        <v>3635.75</v>
+        <v>960.4</v>
       </c>
       <c r="E3">
-        <v>66788</v>
+        <v>17514</v>
       </c>
       <c r="F3">
-        <v>392.2</v>
+        <v>90</v>
       </c>
       <c r="G3">
-        <v>1033</v>
+        <v>369</v>
       </c>
       <c r="H3">
-        <v>972</v>
+        <v>510</v>
       </c>
     </row>
   </sheetData>
@@ -554,19 +557,19 @@
         <v>14</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>18</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -577,22 +580,22 @@
         <v>19</v>
       </c>
       <c r="C2">
-        <v>54450</v>
+        <v>9800</v>
       </c>
       <c r="D2">
-        <v>47342</v>
+        <v>490</v>
       </c>
       <c r="E2">
-        <v>390</v>
+        <v>9341</v>
       </c>
       <c r="F2">
-        <v>700</v>
+        <v>50</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>205</v>
       </c>
       <c r="H2">
-        <v>2722.5</v>
+        <v>510</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -603,100 +606,100 @@
         <v>20</v>
       </c>
       <c r="C3">
-        <v>1796</v>
+        <v>2660</v>
       </c>
       <c r="D3">
-        <v>1796</v>
+        <v>133</v>
       </c>
       <c r="E3">
+        <v>2160</v>
+      </c>
+      <c r="F3">
         <v>9.199999999999999</v>
       </c>
-      <c r="F3">
-        <v>35</v>
-      </c>
       <c r="G3">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="H3">
-        <v>89.8</v>
+        <v>68.40000000000001</v>
       </c>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B4" t="s">
         <v>21</v>
       </c>
       <c r="C4">
-        <v>27048</v>
+        <v>2378</v>
       </c>
       <c r="D4">
-        <v>24832</v>
+        <v>118.9</v>
       </c>
       <c r="E4">
-        <v>120</v>
+        <v>2378</v>
       </c>
       <c r="F4">
-        <v>492</v>
+        <v>15.6</v>
       </c>
       <c r="G4">
-        <v>306</v>
+        <v>28</v>
       </c>
       <c r="H4">
-        <v>1352.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B5" t="s">
         <v>22</v>
       </c>
       <c r="C5">
-        <v>8640</v>
+        <v>980</v>
       </c>
       <c r="D5">
-        <v>8154</v>
+        <v>49</v>
       </c>
       <c r="E5">
-        <v>36.8</v>
+        <v>902</v>
       </c>
       <c r="F5">
-        <v>100</v>
+        <v>8.9</v>
       </c>
       <c r="G5">
-        <v>273.6</v>
+        <v>22.45</v>
       </c>
       <c r="H5">
-        <v>432</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B6" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C6">
-        <v>35231</v>
+        <v>898</v>
       </c>
       <c r="D6">
-        <v>32006</v>
+        <v>44.9</v>
       </c>
       <c r="E6">
-        <v>226.2</v>
+        <v>898</v>
       </c>
       <c r="F6">
-        <v>406</v>
+        <v>4.6</v>
       </c>
       <c r="G6">
-        <v>392.4</v>
+        <v>17.5</v>
       </c>
       <c r="H6">
-        <v>1761.55</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -704,25 +707,25 @@
         <v>11</v>
       </c>
       <c r="B7" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C7">
-        <v>1796</v>
+        <v>19208</v>
       </c>
       <c r="D7">
-        <v>1796</v>
+        <v>960.4</v>
       </c>
       <c r="E7">
-        <v>9.199999999999999</v>
+        <v>17514</v>
       </c>
       <c r="F7">
-        <v>35</v>
+        <v>90</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>369</v>
       </c>
       <c r="H7">
-        <v>89.8</v>
+        <v>510</v>
       </c>
     </row>
   </sheetData>
@@ -732,12 +735,12 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>10</v>
@@ -751,54 +754,65 @@
         <v>19</v>
       </c>
       <c r="B2">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="C2">
-        <v>29</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B3">
         <v>2</v>
       </c>
       <c r="C3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B4">
+        <v>2</v>
+      </c>
+      <c r="C4">
         <v>0</v>
-      </c>
-      <c r="C4">
-        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="C5">
         <v>0</v>
-      </c>
-      <c r="C5">
-        <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B6">
-        <v>52</v>
+        <v>1</v>
       </c>
       <c r="C6">
-        <v>51</v>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B7">
+        <v>11</v>
+      </c>
+      <c r="C7">
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -808,62 +822,63 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
+      <c r="D1" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
         <v>19</v>
       </c>
       <c r="B2">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C2">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
+        <v>10</v>
+      </c>
+      <c r="D2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B3">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="C3">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
+        <v>0</v>
+      </c>
+      <c r="D3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B4">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="C4">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4">
         <v>24</v>
-      </c>
-      <c r="B5">
-        <v>40</v>
-      </c>
-      <c r="C5">
-        <v>40</v>
       </c>
     </row>
   </sheetData>

--- a/sum_daily_order/result/Weekly_Performance_Report_JP_local.xlsx
+++ b/sum_daily_order/result/Weekly_Performance_Report_JP_local.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="29">
   <si>
     <t>文件名称</t>
   </si>
@@ -49,10 +49,16 @@
     <t>0303.csv</t>
   </si>
   <si>
+    <t>0304.csv</t>
+  </si>
+  <si>
     <t>2026-03-02</t>
   </si>
   <si>
     <t>2026-03-03</t>
+  </si>
+  <si>
+    <t>2026-03-04</t>
   </si>
   <si>
     <t>日期</t>
@@ -455,7 +461,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -489,7 +495,7 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C2">
         <v>16716</v>
@@ -515,7 +521,7 @@
         <v>9</v>
       </c>
       <c r="B3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C3">
         <v>19208</v>
@@ -534,6 +540,32 @@
       </c>
       <c r="H3">
         <v>510</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4">
+        <v>20789</v>
+      </c>
+      <c r="D4">
+        <v>1039.45</v>
+      </c>
+      <c r="E4">
+        <v>18813</v>
+      </c>
+      <c r="F4">
+        <v>109.2</v>
+      </c>
+      <c r="G4">
+        <v>315.5</v>
+      </c>
+      <c r="H4">
+        <v>636.1</v>
       </c>
     </row>
   </sheetData>
@@ -543,41 +575,41 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C2">
         <v>9800</v>
@@ -600,10 +632,10 @@
     </row>
     <row r="3" spans="1:8">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C3">
         <v>2660</v>
@@ -626,10 +658,10 @@
     </row>
     <row r="4" spans="1:8">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C4">
         <v>2378</v>
@@ -652,10 +684,10 @@
     </row>
     <row r="5" spans="1:8">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C5">
         <v>980</v>
@@ -678,10 +710,10 @@
     </row>
     <row r="6" spans="1:8">
       <c r="A6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C6">
         <v>898</v>
@@ -704,10 +736,10 @@
     </row>
     <row r="7" spans="1:8">
       <c r="A7" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B7" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C7">
         <v>19208</v>
@@ -726,6 +758,84 @@
       </c>
       <c r="H7">
         <v>510</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8" t="s">
+        <v>21</v>
+      </c>
+      <c r="C8">
+        <v>12936</v>
+      </c>
+      <c r="D8">
+        <v>646.8</v>
+      </c>
+      <c r="E8">
+        <v>11791</v>
+      </c>
+      <c r="F8">
+        <v>50</v>
+      </c>
+      <c r="G8">
+        <v>205</v>
+      </c>
+      <c r="H8">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" t="s">
+        <v>13</v>
+      </c>
+      <c r="B9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C9">
+        <v>1080</v>
+      </c>
+      <c r="D9">
+        <v>54</v>
+      </c>
+      <c r="E9">
+        <v>1080</v>
+      </c>
+      <c r="F9">
+        <v>4.6</v>
+      </c>
+      <c r="G9">
+        <v>12.5</v>
+      </c>
+      <c r="H9">
+        <v>17.1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" t="s">
+        <v>13</v>
+      </c>
+      <c r="B10" t="s">
+        <v>23</v>
+      </c>
+      <c r="C10">
+        <v>6773</v>
+      </c>
+      <c r="D10">
+        <v>338.65</v>
+      </c>
+      <c r="E10">
+        <v>5942</v>
+      </c>
+      <c r="F10">
+        <v>54.6</v>
+      </c>
+      <c r="G10">
+        <v>98</v>
+      </c>
+      <c r="H10">
+        <v>109</v>
       </c>
     </row>
   </sheetData>
@@ -735,45 +845,54 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
+        <v>12</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C2">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
+        <v>0</v>
+      </c>
+      <c r="D2">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
         <v>21</v>
       </c>
       <c r="B3">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
+        <v>9</v>
+      </c>
+      <c r="D3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B4">
         <v>2</v>
@@ -781,10 +900,13 @@
       <c r="C4">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:3">
+      <c r="D4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B5">
         <v>1</v>
@@ -792,10 +914,13 @@
       <c r="C5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:3">
+      <c r="D5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B6">
         <v>1</v>
@@ -803,16 +928,22 @@
       <c r="C6">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:3">
+      <c r="D6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B7">
         <v>11</v>
       </c>
       <c r="C7">
         <v>9</v>
+      </c>
+      <c r="D7">
+        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -822,26 +953,29 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4">
+        <v>13</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
       <c r="A2" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B2">
         <v>10</v>
@@ -850,12 +984,15 @@
         <v>10</v>
       </c>
       <c r="D2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
+        <v>10</v>
+      </c>
+      <c r="E2">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
       <c r="A3" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B3">
         <v>4</v>
@@ -864,21 +1001,44 @@
         <v>0</v>
       </c>
       <c r="D3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
+        <v>1</v>
+      </c>
+      <c r="E3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
       <c r="A4" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B4">
+        <v>0</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+      <c r="D4">
+        <v>5</v>
+      </c>
+      <c r="E4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B5">
         <v>14</v>
       </c>
-      <c r="C4">
+      <c r="C5">
         <v>10</v>
       </c>
-      <c r="D4">
-        <v>24</v>
+      <c r="D5">
+        <v>16</v>
+      </c>
+      <c r="E5">
+        <v>40</v>
       </c>
     </row>
   </sheetData>

--- a/sum_daily_order/result/Weekly_Performance_Report_JP_local.xlsx
+++ b/sum_daily_order/result/Weekly_Performance_Report_JP_local.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="29">
   <si>
     <t>文件名称</t>
   </si>
@@ -43,22 +43,28 @@
     <t>寄样总支出(含物流)</t>
   </si>
   <si>
-    <t>0302.csv</t>
-  </si>
-  <si>
-    <t>0303.csv</t>
-  </si>
-  <si>
-    <t>0304.csv</t>
-  </si>
-  <si>
-    <t>2026-03-02</t>
-  </si>
-  <si>
-    <t>2026-03-03</t>
-  </si>
-  <si>
-    <t>2026-03-04</t>
+    <t>0308.csv</t>
+  </si>
+  <si>
+    <t>0309.csv</t>
+  </si>
+  <si>
+    <t>0310.csv</t>
+  </si>
+  <si>
+    <t>0311.csv</t>
+  </si>
+  <si>
+    <t>2026-03-08</t>
+  </si>
+  <si>
+    <t>2026-03-09</t>
+  </si>
+  <si>
+    <t>2026-03-10</t>
+  </si>
+  <si>
+    <t>2026-03-11</t>
   </si>
   <si>
     <t>日期</t>
@@ -89,12 +95,6 @@
   </si>
   <si>
     <t>电动鼻毛刀</t>
-  </si>
-  <si>
-    <t>白色睫毛推</t>
-  </si>
-  <si>
-    <t>车载手机支架</t>
   </si>
   <si>
     <t>商品名称</t>
@@ -461,7 +461,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -495,25 +495,25 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C2">
-        <v>16716</v>
+        <v>27304</v>
       </c>
       <c r="D2">
-        <v>835.8</v>
+        <v>1365.2</v>
       </c>
       <c r="E2">
-        <v>15679</v>
+        <v>25520</v>
       </c>
       <c r="F2">
-        <v>88.3</v>
+        <v>135.8</v>
       </c>
       <c r="G2">
-        <v>297.95</v>
+        <v>478.5</v>
       </c>
       <c r="H2">
-        <v>578.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -521,25 +521,25 @@
         <v>9</v>
       </c>
       <c r="B3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C3">
-        <v>19208</v>
+        <v>27588</v>
       </c>
       <c r="D3">
-        <v>960.4</v>
+        <v>1379.4</v>
       </c>
       <c r="E3">
-        <v>17514</v>
+        <v>25598</v>
       </c>
       <c r="F3">
-        <v>90</v>
+        <v>105.8</v>
       </c>
       <c r="G3">
-        <v>369</v>
+        <v>355.5</v>
       </c>
       <c r="H3">
-        <v>510</v>
+        <v>116.7</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -547,25 +547,51 @@
         <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C4">
-        <v>20789</v>
+        <v>33291</v>
       </c>
       <c r="D4">
-        <v>1039.45</v>
+        <v>1664.55</v>
       </c>
       <c r="E4">
-        <v>18813</v>
+        <v>28460</v>
       </c>
       <c r="F4">
-        <v>109.2</v>
+        <v>137.8</v>
       </c>
       <c r="G4">
-        <v>315.5</v>
+        <v>547</v>
       </c>
       <c r="H4">
-        <v>636.1</v>
+        <v>119.1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5">
+        <v>26020</v>
+      </c>
+      <c r="D5">
+        <v>1301</v>
+      </c>
+      <c r="E5">
+        <v>22898</v>
+      </c>
+      <c r="F5">
+        <v>95.8</v>
+      </c>
+      <c r="G5">
+        <v>314.5</v>
+      </c>
+      <c r="H5">
+        <v>201.6</v>
       </c>
     </row>
   </sheetData>
@@ -575,108 +601,108 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:H13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C2">
-        <v>9800</v>
+        <v>22168</v>
       </c>
       <c r="D2">
-        <v>490</v>
+        <v>1108.4</v>
       </c>
       <c r="E2">
-        <v>9341</v>
+        <v>20384</v>
       </c>
       <c r="F2">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="G2">
-        <v>205</v>
+        <v>410</v>
       </c>
       <c r="H2">
-        <v>510</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C3">
-        <v>2660</v>
+        <v>980</v>
       </c>
       <c r="D3">
-        <v>133</v>
+        <v>49</v>
       </c>
       <c r="E3">
-        <v>2160</v>
+        <v>980</v>
       </c>
       <c r="F3">
-        <v>9.199999999999999</v>
+        <v>4.6</v>
       </c>
       <c r="G3">
-        <v>25</v>
+        <v>12.5</v>
       </c>
       <c r="H3">
-        <v>68.40000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B4" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C4">
-        <v>2378</v>
+        <v>4156</v>
       </c>
       <c r="D4">
-        <v>118.9</v>
+        <v>207.8</v>
       </c>
       <c r="E4">
-        <v>2378</v>
+        <v>4156</v>
       </c>
       <c r="F4">
-        <v>15.6</v>
+        <v>31.2</v>
       </c>
       <c r="G4">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c r="H4">
         <v>0</v>
@@ -684,25 +710,25 @@
     </row>
     <row r="5" spans="1:8">
       <c r="A5" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C5">
-        <v>980</v>
+        <v>22452</v>
       </c>
       <c r="D5">
-        <v>49</v>
+        <v>1122.6</v>
       </c>
       <c r="E5">
-        <v>902</v>
+        <v>20462</v>
       </c>
       <c r="F5">
-        <v>8.9</v>
+        <v>70</v>
       </c>
       <c r="G5">
-        <v>22.45</v>
+        <v>287</v>
       </c>
       <c r="H5">
         <v>0</v>
@@ -710,103 +736,103 @@
     </row>
     <row r="6" spans="1:8">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C6">
-        <v>898</v>
+        <v>980</v>
       </c>
       <c r="D6">
-        <v>44.9</v>
+        <v>49</v>
       </c>
       <c r="E6">
-        <v>898</v>
+        <v>980</v>
       </c>
       <c r="F6">
         <v>4.6</v>
       </c>
       <c r="G6">
-        <v>17.5</v>
+        <v>12.5</v>
       </c>
       <c r="H6">
-        <v>0</v>
+        <v>51.3</v>
       </c>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B7" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C7">
-        <v>19208</v>
+        <v>4156</v>
       </c>
       <c r="D7">
-        <v>960.4</v>
+        <v>207.8</v>
       </c>
       <c r="E7">
-        <v>17514</v>
+        <v>4156</v>
       </c>
       <c r="F7">
-        <v>90</v>
+        <v>31.2</v>
       </c>
       <c r="G7">
-        <v>369</v>
+        <v>56</v>
       </c>
       <c r="H7">
-        <v>510</v>
+        <v>65.40000000000001</v>
       </c>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C8">
-        <v>12936</v>
+        <v>32252</v>
       </c>
       <c r="D8">
-        <v>646.8</v>
+        <v>1612.6</v>
       </c>
       <c r="E8">
-        <v>11791</v>
+        <v>27421</v>
       </c>
       <c r="F8">
-        <v>50</v>
+        <v>130</v>
       </c>
       <c r="G8">
-        <v>205</v>
+        <v>533</v>
       </c>
       <c r="H8">
-        <v>510</v>
+        <v>102</v>
       </c>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C9">
-        <v>1080</v>
+        <v>0</v>
       </c>
       <c r="D9">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="E9">
-        <v>1080</v>
+        <v>0</v>
       </c>
       <c r="F9">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="G9">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="H9">
         <v>17.1</v>
@@ -814,28 +840,106 @@
     </row>
     <row r="10" spans="1:8">
       <c r="A10" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B10" t="s">
+        <v>25</v>
+      </c>
+      <c r="C10">
+        <v>1039</v>
+      </c>
+      <c r="D10">
+        <v>51.95</v>
+      </c>
+      <c r="E10">
+        <v>1039</v>
+      </c>
+      <c r="F10">
+        <v>7.8</v>
+      </c>
+      <c r="G10">
+        <v>14</v>
+      </c>
+      <c r="H10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="A11" t="s">
+        <v>15</v>
+      </c>
+      <c r="B11" t="s">
         <v>23</v>
       </c>
-      <c r="C10">
-        <v>6773</v>
-      </c>
-      <c r="D10">
-        <v>338.65</v>
-      </c>
-      <c r="E10">
-        <v>5942</v>
-      </c>
-      <c r="F10">
-        <v>54.6</v>
-      </c>
-      <c r="G10">
-        <v>98</v>
-      </c>
-      <c r="H10">
-        <v>109</v>
+      <c r="C11">
+        <v>20884</v>
+      </c>
+      <c r="D11">
+        <v>1044.2</v>
+      </c>
+      <c r="E11">
+        <v>18053</v>
+      </c>
+      <c r="F11">
+        <v>60</v>
+      </c>
+      <c r="G11">
+        <v>246</v>
+      </c>
+      <c r="H11">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
+      <c r="A12" t="s">
+        <v>15</v>
+      </c>
+      <c r="B12" t="s">
+        <v>24</v>
+      </c>
+      <c r="C12">
+        <v>980</v>
+      </c>
+      <c r="D12">
+        <v>49</v>
+      </c>
+      <c r="E12">
+        <v>980</v>
+      </c>
+      <c r="F12">
+        <v>4.6</v>
+      </c>
+      <c r="G12">
+        <v>12.5</v>
+      </c>
+      <c r="H12">
+        <v>34.2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
+      <c r="A13" t="s">
+        <v>15</v>
+      </c>
+      <c r="B13" t="s">
+        <v>25</v>
+      </c>
+      <c r="C13">
+        <v>4156</v>
+      </c>
+      <c r="D13">
+        <v>207.8</v>
+      </c>
+      <c r="E13">
+        <v>3865</v>
+      </c>
+      <c r="F13">
+        <v>31.2</v>
+      </c>
+      <c r="G13">
+        <v>56</v>
+      </c>
+      <c r="H13">
+        <v>65.40000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -845,105 +949,92 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
         <v>26</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4">
+        <v>14</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
       <c r="A2" s="1" t="s">
         <v>23</v>
       </c>
       <c r="B2">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C2">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D2">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
+        <v>13</v>
+      </c>
+      <c r="E2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
       <c r="A3" s="1" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C3">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
+        <v>1</v>
+      </c>
+      <c r="E3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
       <c r="A4" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:4">
+    <row r="5" spans="1:5">
       <c r="A5" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B5">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="C5">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="D5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
-      <c r="A6" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B6">
-        <v>1</v>
-      </c>
-      <c r="C6">
-        <v>0</v>
-      </c>
-      <c r="D6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4">
-      <c r="A7" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B7">
+        <v>14</v>
+      </c>
+      <c r="E5">
         <v>11</v>
-      </c>
-      <c r="C7">
-        <v>9</v>
-      </c>
-      <c r="D7">
-        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -961,13 +1052,13 @@
         <v>26</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>28</v>
@@ -975,36 +1066,36 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="B2">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C2">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D2">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="E2">
-        <v>30</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="1" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="B3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C3">
         <v>0</v>
       </c>
       <c r="D3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E3">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -1015,13 +1106,13 @@
         <v>0</v>
       </c>
       <c r="C4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D4">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E4">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -1029,16 +1120,16 @@
         <v>27</v>
       </c>
       <c r="B5">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="C5">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D5">
+        <v>7</v>
+      </c>
+      <c r="E5">
         <v>16</v>
-      </c>
-      <c r="E5">
-        <v>40</v>
       </c>
     </row>
   </sheetData>

--- a/sum_daily_order/result/Weekly_Performance_Report_JP_local.xlsx
+++ b/sum_daily_order/result/Weekly_Performance_Report_JP_local.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="29">
   <si>
     <t>文件名称</t>
   </si>
@@ -43,28 +43,16 @@
     <t>寄样总支出(含物流)</t>
   </si>
   <si>
-    <t>0308.csv</t>
-  </si>
-  <si>
-    <t>0309.csv</t>
-  </si>
-  <si>
-    <t>0310.csv</t>
-  </si>
-  <si>
-    <t>0311.csv</t>
+    <t>本土店-0308.csv</t>
+  </si>
+  <si>
+    <t>本土店-0315.csv</t>
   </si>
   <si>
     <t>2026-03-08</t>
   </si>
   <si>
-    <t>2026-03-09</t>
-  </si>
-  <si>
-    <t>2026-03-10</t>
-  </si>
-  <si>
-    <t>2026-03-11</t>
+    <t>2026-03-15</t>
   </si>
   <si>
     <t>日期</t>
@@ -88,6 +76,9 @@
     <t>寄样支出</t>
   </si>
   <si>
+    <t>其他</t>
+  </si>
+  <si>
     <t>头发护理精华</t>
   </si>
   <si>
@@ -97,7 +88,16 @@
     <t>电动鼻毛刀</t>
   </si>
   <si>
+    <t>白色睫毛推</t>
+  </si>
+  <si>
+    <t>车载手机支架</t>
+  </si>
+  <si>
     <t>商品名称</t>
+  </si>
+  <si>
+    <t>发饰水银11点</t>
   </si>
   <si>
     <t>汇总</t>
@@ -461,7 +461,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -495,25 +495,25 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C2">
-        <v>27304</v>
+        <v>120520</v>
       </c>
       <c r="D2">
-        <v>1365.2</v>
+        <v>6026</v>
       </c>
       <c r="E2">
-        <v>25520</v>
+        <v>110341</v>
       </c>
       <c r="F2">
-        <v>135.8</v>
+        <v>643.5</v>
       </c>
       <c r="G2">
-        <v>478.5</v>
+        <v>2019.95</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>2620.6</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -521,77 +521,25 @@
         <v>9</v>
       </c>
       <c r="B3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C3">
-        <v>27588</v>
+        <v>223623</v>
       </c>
       <c r="D3">
-        <v>1379.4</v>
+        <v>11181.15</v>
       </c>
       <c r="E3">
-        <v>25598</v>
+        <v>197564</v>
       </c>
       <c r="F3">
-        <v>105.8</v>
+        <v>1097.6</v>
       </c>
       <c r="G3">
-        <v>355.5</v>
+        <v>3203.5</v>
       </c>
       <c r="H3">
-        <v>116.7</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8">
-      <c r="A4" t="s">
-        <v>10</v>
-      </c>
-      <c r="B4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C4">
-        <v>33291</v>
-      </c>
-      <c r="D4">
-        <v>1664.55</v>
-      </c>
-      <c r="E4">
-        <v>28460</v>
-      </c>
-      <c r="F4">
-        <v>137.8</v>
-      </c>
-      <c r="G4">
-        <v>547</v>
-      </c>
-      <c r="H4">
-        <v>119.1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8">
-      <c r="A5" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5" t="s">
-        <v>15</v>
-      </c>
-      <c r="C5">
-        <v>26020</v>
-      </c>
-      <c r="D5">
-        <v>1301</v>
-      </c>
-      <c r="E5">
-        <v>22898</v>
-      </c>
-      <c r="F5">
-        <v>95.8</v>
-      </c>
-      <c r="G5">
-        <v>314.5</v>
-      </c>
-      <c r="H5">
-        <v>201.6</v>
+        <v>942.6</v>
       </c>
     </row>
   </sheetData>
@@ -601,56 +549,56 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C2">
-        <v>22168</v>
+        <v>1900</v>
       </c>
       <c r="D2">
-        <v>1108.4</v>
+        <v>95</v>
       </c>
       <c r="E2">
-        <v>20384</v>
+        <v>1400</v>
       </c>
       <c r="F2">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G2">
-        <v>410</v>
+        <v>0</v>
       </c>
       <c r="H2">
         <v>0</v>
@@ -658,88 +606,88 @@
     </row>
     <row r="3" spans="1:8">
       <c r="A3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C3">
-        <v>980</v>
+        <v>76372</v>
       </c>
       <c r="D3">
-        <v>49</v>
+        <v>3818.6</v>
       </c>
       <c r="E3">
-        <v>980</v>
+        <v>68799</v>
       </c>
       <c r="F3">
-        <v>4.6</v>
+        <v>350</v>
       </c>
       <c r="G3">
-        <v>12.5</v>
+        <v>1435</v>
       </c>
       <c r="H3">
-        <v>0</v>
+        <v>2244</v>
       </c>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C4">
-        <v>4156</v>
+        <v>10600</v>
       </c>
       <c r="D4">
-        <v>207.8</v>
+        <v>530</v>
       </c>
       <c r="E4">
-        <v>4156</v>
+        <v>10041</v>
       </c>
       <c r="F4">
-        <v>31.2</v>
+        <v>46</v>
       </c>
       <c r="G4">
-        <v>56</v>
+        <v>125</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>136.8</v>
       </c>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C5">
-        <v>22452</v>
+        <v>29770</v>
       </c>
       <c r="D5">
-        <v>1122.6</v>
+        <v>1488.5</v>
       </c>
       <c r="E5">
-        <v>20462</v>
+        <v>28301</v>
       </c>
       <c r="F5">
-        <v>70</v>
+        <v>234</v>
       </c>
       <c r="G5">
-        <v>287</v>
+        <v>420</v>
       </c>
       <c r="H5">
-        <v>0</v>
+        <v>239.8</v>
       </c>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C6">
         <v>980</v>
@@ -748,198 +696,146 @@
         <v>49</v>
       </c>
       <c r="E6">
-        <v>980</v>
+        <v>902</v>
       </c>
       <c r="F6">
-        <v>4.6</v>
+        <v>8.9</v>
       </c>
       <c r="G6">
-        <v>12.5</v>
+        <v>22.45</v>
       </c>
       <c r="H6">
-        <v>51.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B7" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C7">
-        <v>4156</v>
+        <v>898</v>
       </c>
       <c r="D7">
-        <v>207.8</v>
+        <v>44.9</v>
       </c>
       <c r="E7">
-        <v>4156</v>
+        <v>898</v>
       </c>
       <c r="F7">
-        <v>31.2</v>
+        <v>4.6</v>
       </c>
       <c r="G7">
-        <v>56</v>
+        <v>17.5</v>
       </c>
       <c r="H7">
-        <v>65.40000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B8" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C8">
-        <v>32252</v>
+        <v>125088</v>
       </c>
       <c r="D8">
-        <v>1612.6</v>
+        <v>6254.4</v>
       </c>
       <c r="E8">
-        <v>27421</v>
+        <v>106560</v>
       </c>
       <c r="F8">
-        <v>130</v>
+        <v>470</v>
       </c>
       <c r="G8">
-        <v>533</v>
+        <v>1927</v>
       </c>
       <c r="H8">
-        <v>102</v>
+        <v>510</v>
       </c>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C9">
-        <v>0</v>
+        <v>31860</v>
       </c>
       <c r="D9">
-        <v>0</v>
+        <v>1593</v>
       </c>
       <c r="E9">
-        <v>0</v>
+        <v>31222</v>
       </c>
       <c r="F9">
-        <v>0</v>
+        <v>142.6</v>
       </c>
       <c r="G9">
-        <v>0</v>
+        <v>387.5</v>
       </c>
       <c r="H9">
-        <v>17.1</v>
+        <v>171</v>
       </c>
     </row>
     <row r="10" spans="1:8">
       <c r="A10" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B10" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C10">
-        <v>1039</v>
+        <v>64379</v>
       </c>
       <c r="D10">
-        <v>51.95</v>
+        <v>3218.95</v>
       </c>
       <c r="E10">
-        <v>1039</v>
+        <v>57986</v>
       </c>
       <c r="F10">
-        <v>7.8</v>
+        <v>475.8</v>
       </c>
       <c r="G10">
-        <v>14</v>
+        <v>854</v>
       </c>
       <c r="H10">
-        <v>0</v>
+        <v>261.6</v>
       </c>
     </row>
     <row r="11" spans="1:8">
       <c r="A11" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="B11" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C11">
-        <v>20884</v>
+        <v>2296</v>
       </c>
       <c r="D11">
-        <v>1044.2</v>
+        <v>114.8</v>
       </c>
       <c r="E11">
-        <v>18053</v>
+        <v>1796</v>
       </c>
       <c r="F11">
-        <v>60</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="G11">
-        <v>246</v>
+        <v>35</v>
       </c>
       <c r="H11">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8">
-      <c r="A12" t="s">
-        <v>15</v>
-      </c>
-      <c r="B12" t="s">
-        <v>24</v>
-      </c>
-      <c r="C12">
-        <v>980</v>
-      </c>
-      <c r="D12">
-        <v>49</v>
-      </c>
-      <c r="E12">
-        <v>980</v>
-      </c>
-      <c r="F12">
-        <v>4.6</v>
-      </c>
-      <c r="G12">
-        <v>12.5</v>
-      </c>
-      <c r="H12">
-        <v>34.2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8">
-      <c r="A13" t="s">
-        <v>15</v>
-      </c>
-      <c r="B13" t="s">
-        <v>25</v>
-      </c>
-      <c r="C13">
-        <v>4156</v>
-      </c>
-      <c r="D13">
-        <v>207.8</v>
-      </c>
-      <c r="E13">
-        <v>3865</v>
-      </c>
-      <c r="F13">
-        <v>31.2</v>
-      </c>
-      <c r="G13">
-        <v>56</v>
-      </c>
-      <c r="H13">
-        <v>65.40000000000001</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -949,92 +845,95 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B2">
+        <v>30</v>
+      </c>
+      <c r="C2">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B3">
+        <v>35</v>
+      </c>
+      <c r="C3">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4">
+        <v>10</v>
+      </c>
+      <c r="C4">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="C5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2" s="1" t="s">
+      <c r="B6">
+        <v>1</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B2">
-        <v>10</v>
-      </c>
-      <c r="C2">
-        <v>7</v>
-      </c>
-      <c r="D2">
-        <v>13</v>
-      </c>
-      <c r="E2">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B3">
-        <v>4</v>
-      </c>
-      <c r="C3">
-        <v>4</v>
-      </c>
-      <c r="D3">
+      <c r="B7">
         <v>1</v>
       </c>
-      <c r="E3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-      <c r="C4">
-        <v>1</v>
-      </c>
-      <c r="D4">
+      <c r="C7">
         <v>0</v>
       </c>
-      <c r="E4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="A5" s="1" t="s">
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B5">
-        <v>15</v>
-      </c>
-      <c r="C5">
-        <v>12</v>
-      </c>
-      <c r="D5">
-        <v>14</v>
-      </c>
-      <c r="E5">
-        <v>11</v>
+      <c r="B8">
+        <v>78</v>
+      </c>
+      <c r="C8">
+        <v>141</v>
       </c>
     </row>
   </sheetData>
@@ -1044,92 +943,77 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E1" s="1" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="B2">
-        <v>3</v>
+        <v>44</v>
       </c>
       <c r="C2">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D2">
-        <v>2</v>
-      </c>
-      <c r="E2">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B3">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C3">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="D3">
-        <v>3</v>
-      </c>
-      <c r="E3">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B4">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="C4">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D4">
-        <v>2</v>
-      </c>
-      <c r="E4">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
         <v>27</v>
       </c>
       <c r="B5">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="C5">
-        <v>3</v>
+        <v>32</v>
       </c>
       <c r="D5">
-        <v>7</v>
-      </c>
-      <c r="E5">
-        <v>16</v>
+        <v>95</v>
       </c>
     </row>
   </sheetData>

--- a/sum_daily_order/result/Weekly_Performance_Report_JP_local.xlsx
+++ b/sum_daily_order/result/Weekly_Performance_Report_JP_local.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="26">
   <si>
     <t>文件名称</t>
   </si>
@@ -43,16 +43,16 @@
     <t>寄样总支出(含物流)</t>
   </si>
   <si>
-    <t>本土店-0308.csv</t>
-  </si>
-  <si>
-    <t>本土店-0315.csv</t>
-  </si>
-  <si>
-    <t>2026-03-08</t>
-  </si>
-  <si>
-    <t>2026-03-15</t>
+    <t>0316.csv</t>
+  </si>
+  <si>
+    <t>0317.csv</t>
+  </si>
+  <si>
+    <t>2026-03-16</t>
+  </si>
+  <si>
+    <t>2026-03-17</t>
   </si>
   <si>
     <t>日期</t>
@@ -79,25 +79,16 @@
     <t>其他</t>
   </si>
   <si>
-    <t>头发护理精华</t>
-  </si>
-  <si>
     <t>电动剃眉刀</t>
   </si>
   <si>
     <t>电动鼻毛刀</t>
   </si>
   <si>
-    <t>白色睫毛推</t>
-  </si>
-  <si>
-    <t>车载手机支架</t>
-  </si>
-  <si>
     <t>商品名称</t>
   </si>
   <si>
-    <t>发饰水银11点</t>
+    <t>【公式】スムースリペア ヘアブースター 290g | 幻のサロン専売品がついに解禁！シャンプーに混ぜるだけの新習慣 髪の美容液 導入液 ダメージ補修 うねり・パサつき改善</t>
   </si>
   <si>
     <t>汇总</t>
@@ -498,22 +489,22 @@
         <v>10</v>
       </c>
       <c r="C2">
-        <v>120520</v>
+        <v>23718</v>
       </c>
       <c r="D2">
-        <v>6026</v>
+        <v>1185.9</v>
       </c>
       <c r="E2">
-        <v>110341</v>
+        <v>22540</v>
       </c>
       <c r="F2">
-        <v>643.5</v>
+        <v>114.8</v>
       </c>
       <c r="G2">
-        <v>2019.95</v>
+        <v>240</v>
       </c>
       <c r="H2">
-        <v>2620.6</v>
+        <v>77.8</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -524,22 +515,22 @@
         <v>11</v>
       </c>
       <c r="C3">
-        <v>223623</v>
+        <v>10713</v>
       </c>
       <c r="D3">
-        <v>11181.15</v>
+        <v>535.65</v>
       </c>
       <c r="E3">
-        <v>197564</v>
+        <v>9767</v>
       </c>
       <c r="F3">
-        <v>1097.6</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="G3">
-        <v>3203.5</v>
+        <v>135.5</v>
       </c>
       <c r="H3">
-        <v>942.6</v>
+        <v>99.59999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -549,7 +540,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -586,13 +577,13 @@
         <v>19</v>
       </c>
       <c r="C2">
-        <v>1900</v>
+        <v>5488</v>
       </c>
       <c r="D2">
-        <v>95</v>
+        <v>274.4</v>
       </c>
       <c r="E2">
-        <v>1400</v>
+        <v>5135</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -612,22 +603,22 @@
         <v>20</v>
       </c>
       <c r="C3">
-        <v>76372</v>
+        <v>7840</v>
       </c>
       <c r="D3">
-        <v>3818.6</v>
+        <v>392</v>
       </c>
       <c r="E3">
-        <v>68799</v>
+        <v>7379</v>
       </c>
       <c r="F3">
-        <v>350</v>
+        <v>36.8</v>
       </c>
       <c r="G3">
-        <v>1435</v>
+        <v>100</v>
       </c>
       <c r="H3">
-        <v>2244</v>
+        <v>34.2</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -638,204 +629,74 @@
         <v>21</v>
       </c>
       <c r="C4">
-        <v>10600</v>
+        <v>10390</v>
       </c>
       <c r="D4">
-        <v>530</v>
+        <v>519.5</v>
       </c>
       <c r="E4">
-        <v>10041</v>
+        <v>10026</v>
       </c>
       <c r="F4">
-        <v>46</v>
+        <v>78</v>
       </c>
       <c r="G4">
-        <v>125</v>
+        <v>140</v>
       </c>
       <c r="H4">
-        <v>136.8</v>
+        <v>43.6</v>
       </c>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C5">
-        <v>29770</v>
+        <v>3440</v>
       </c>
       <c r="D5">
-        <v>1488.5</v>
+        <v>172</v>
       </c>
       <c r="E5">
-        <v>28301</v>
+        <v>2940</v>
       </c>
       <c r="F5">
-        <v>234</v>
+        <v>13.8</v>
       </c>
       <c r="G5">
-        <v>420</v>
+        <v>37.5</v>
       </c>
       <c r="H5">
-        <v>239.8</v>
+        <v>34.2</v>
       </c>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C6">
-        <v>980</v>
+        <v>7273</v>
       </c>
       <c r="D6">
-        <v>49</v>
+        <v>363.65</v>
       </c>
       <c r="E6">
-        <v>902</v>
+        <v>6827</v>
       </c>
       <c r="F6">
-        <v>8.9</v>
+        <v>54.6</v>
       </c>
       <c r="G6">
-        <v>22.45</v>
+        <v>98</v>
       </c>
       <c r="H6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8">
-      <c r="A7" t="s">
-        <v>10</v>
-      </c>
-      <c r="B7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C7">
-        <v>898</v>
-      </c>
-      <c r="D7">
-        <v>44.9</v>
-      </c>
-      <c r="E7">
-        <v>898</v>
-      </c>
-      <c r="F7">
-        <v>4.6</v>
-      </c>
-      <c r="G7">
-        <v>17.5</v>
-      </c>
-      <c r="H7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8">
-      <c r="A8" t="s">
-        <v>11</v>
-      </c>
-      <c r="B8" t="s">
-        <v>20</v>
-      </c>
-      <c r="C8">
-        <v>125088</v>
-      </c>
-      <c r="D8">
-        <v>6254.4</v>
-      </c>
-      <c r="E8">
-        <v>106560</v>
-      </c>
-      <c r="F8">
-        <v>470</v>
-      </c>
-      <c r="G8">
-        <v>1927</v>
-      </c>
-      <c r="H8">
-        <v>510</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8">
-      <c r="A9" t="s">
-        <v>11</v>
-      </c>
-      <c r="B9" t="s">
-        <v>21</v>
-      </c>
-      <c r="C9">
-        <v>31860</v>
-      </c>
-      <c r="D9">
-        <v>1593</v>
-      </c>
-      <c r="E9">
-        <v>31222</v>
-      </c>
-      <c r="F9">
-        <v>142.6</v>
-      </c>
-      <c r="G9">
-        <v>387.5</v>
-      </c>
-      <c r="H9">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8">
-      <c r="A10" t="s">
-        <v>11</v>
-      </c>
-      <c r="B10" t="s">
-        <v>22</v>
-      </c>
-      <c r="C10">
-        <v>64379</v>
-      </c>
-      <c r="D10">
-        <v>3218.95</v>
-      </c>
-      <c r="E10">
-        <v>57986</v>
-      </c>
-      <c r="F10">
-        <v>475.8</v>
-      </c>
-      <c r="G10">
-        <v>854</v>
-      </c>
-      <c r="H10">
-        <v>261.6</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8">
-      <c r="A11" t="s">
-        <v>11</v>
-      </c>
-      <c r="B11" t="s">
-        <v>24</v>
-      </c>
-      <c r="C11">
-        <v>2296</v>
-      </c>
-      <c r="D11">
-        <v>114.8</v>
-      </c>
-      <c r="E11">
-        <v>1796</v>
-      </c>
-      <c r="F11">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="G11">
-        <v>35</v>
-      </c>
-      <c r="H11">
-        <v>0</v>
+        <v>65.40000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -845,12 +706,12 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>10</v>
@@ -861,13 +722,13 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B2">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C2">
-        <v>61</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -875,21 +736,21 @@
         <v>20</v>
       </c>
       <c r="B3">
-        <v>35</v>
+        <v>8</v>
       </c>
       <c r="C3">
-        <v>47</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B4">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="C4">
-        <v>31</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -897,43 +758,10 @@
         <v>24</v>
       </c>
       <c r="B5">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="C5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B6">
-        <v>1</v>
-      </c>
-      <c r="C6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B7">
-        <v>1</v>
-      </c>
-      <c r="C7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B8">
-        <v>78</v>
-      </c>
-      <c r="C8">
-        <v>141</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -943,12 +771,12 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>10</v>
@@ -957,63 +785,49 @@
         <v>11</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B2">
-        <v>44</v>
+        <v>2</v>
       </c>
       <c r="C2">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D2">
-        <v>54</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B3">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="C3">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="D3">
-        <v>23</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="B4">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C4">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D4">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
-      <c r="A5" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B5">
-        <v>63</v>
-      </c>
-      <c r="C5">
-        <v>32</v>
-      </c>
-      <c r="D5">
-        <v>95</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/sum_daily_order/result/Weekly_Performance_Report_JP_local.xlsx
+++ b/sum_daily_order/result/Weekly_Performance_Report_JP_local.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="27">
   <si>
     <t>文件名称</t>
   </si>
@@ -43,16 +43,22 @@
     <t>寄样总支出(含物流)</t>
   </si>
   <si>
-    <t>0316.csv</t>
-  </si>
-  <si>
-    <t>0317.csv</t>
-  </si>
-  <si>
-    <t>2026-03-16</t>
-  </si>
-  <si>
-    <t>2026-03-17</t>
+    <t>0329.csv</t>
+  </si>
+  <si>
+    <t>0330.csv</t>
+  </si>
+  <si>
+    <t>0331.csv</t>
+  </si>
+  <si>
+    <t>2026-03-29</t>
+  </si>
+  <si>
+    <t>2026-03-30</t>
+  </si>
+  <si>
+    <t>2026-03-31</t>
   </si>
   <si>
     <t>日期</t>
@@ -76,19 +82,16 @@
     <t>寄样支出</t>
   </si>
   <si>
-    <t>其他</t>
-  </si>
-  <si>
     <t>电动剃眉刀</t>
   </si>
   <si>
     <t>电动鼻毛刀</t>
   </si>
   <si>
-    <t>商品名称</t>
-  </si>
-  <si>
-    <t>【公式】スムースリペア ヘアブースター 290g | 幻のサロン専売品がついに解禁！シャンプーに混ぜるだけの新習慣 髪の美容液 導入液 ダメージ補修 うねり・パサつき改善</t>
+    <t>车载手机支架</t>
+  </si>
+  <si>
+    <t>产品名称</t>
   </si>
   <si>
     <t>汇总</t>
@@ -452,7 +455,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -486,25 +489,25 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C2">
-        <v>23718</v>
+        <v>23101</v>
       </c>
       <c r="D2">
-        <v>1185.9</v>
+        <v>1155.05</v>
       </c>
       <c r="E2">
-        <v>22540</v>
+        <v>21665</v>
       </c>
       <c r="F2">
-        <v>114.8</v>
+        <v>207</v>
       </c>
       <c r="G2">
-        <v>240</v>
+        <v>402</v>
       </c>
       <c r="H2">
-        <v>77.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -512,25 +515,51 @@
         <v>9</v>
       </c>
       <c r="B3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C3">
-        <v>10713</v>
+        <v>24379</v>
       </c>
       <c r="D3">
-        <v>535.65</v>
+        <v>1218.95</v>
       </c>
       <c r="E3">
-        <v>9767</v>
+        <v>22283</v>
       </c>
       <c r="F3">
-        <v>68.40000000000001</v>
+        <v>227.2</v>
       </c>
       <c r="G3">
-        <v>135.5</v>
+        <v>442.5</v>
       </c>
       <c r="H3">
-        <v>99.59999999999999</v>
+        <v>126.1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4">
+        <v>24962</v>
+      </c>
+      <c r="D4">
+        <v>1248.1</v>
+      </c>
+      <c r="E4">
+        <v>21649</v>
+      </c>
+      <c r="F4">
+        <v>230.4</v>
+      </c>
+      <c r="G4">
+        <v>439</v>
+      </c>
+      <c r="H4">
+        <v>121.4</v>
       </c>
     </row>
   </sheetData>
@@ -540,56 +569,56 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C2">
-        <v>5488</v>
+        <v>4680</v>
       </c>
       <c r="D2">
-        <v>274.4</v>
+        <v>234</v>
       </c>
       <c r="E2">
-        <v>5135</v>
+        <v>3606</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>62.5</v>
       </c>
       <c r="H2">
         <v>0</v>
@@ -597,106 +626,184 @@
     </row>
     <row r="3" spans="1:8">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C3">
-        <v>7840</v>
+        <v>17733</v>
       </c>
       <c r="D3">
-        <v>392</v>
+        <v>886.65</v>
       </c>
       <c r="E3">
-        <v>7379</v>
+        <v>17371</v>
       </c>
       <c r="F3">
-        <v>36.8</v>
+        <v>179.4</v>
       </c>
       <c r="G3">
-        <v>100</v>
+        <v>322</v>
       </c>
       <c r="H3">
-        <v>34.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C4">
-        <v>10390</v>
+        <v>688</v>
       </c>
       <c r="D4">
-        <v>519.5</v>
+        <v>34.4</v>
       </c>
       <c r="E4">
-        <v>10026</v>
+        <v>688</v>
       </c>
       <c r="F4">
-        <v>78</v>
+        <v>4.6</v>
       </c>
       <c r="G4">
-        <v>140</v>
+        <v>17.5</v>
       </c>
       <c r="H4">
-        <v>43.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C5">
-        <v>3440</v>
+        <v>4416</v>
       </c>
       <c r="D5">
-        <v>172</v>
+        <v>220.8</v>
       </c>
       <c r="E5">
-        <v>2940</v>
+        <v>4049</v>
       </c>
       <c r="F5">
-        <v>13.8</v>
+        <v>27.6</v>
       </c>
       <c r="G5">
-        <v>37.5</v>
+        <v>75</v>
       </c>
       <c r="H5">
-        <v>34.2</v>
+        <v>17.1</v>
       </c>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6">
+        <v>19275</v>
+      </c>
+      <c r="D6">
+        <v>963.75</v>
+      </c>
+      <c r="E6">
+        <v>17752</v>
+      </c>
+      <c r="F6">
+        <v>195</v>
+      </c>
+      <c r="G6">
+        <v>350</v>
+      </c>
+      <c r="H6">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" t="s">
+        <v>23</v>
+      </c>
+      <c r="C7">
+        <v>688</v>
+      </c>
+      <c r="D7">
+        <v>34.4</v>
+      </c>
+      <c r="E7">
+        <v>482</v>
+      </c>
+      <c r="F7">
+        <v>4.6</v>
+      </c>
+      <c r="G7">
+        <v>17.5</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8" t="s">
         <v>21</v>
       </c>
-      <c r="C6">
-        <v>7273</v>
-      </c>
-      <c r="D6">
-        <v>363.65</v>
-      </c>
-      <c r="E6">
-        <v>6827</v>
-      </c>
-      <c r="F6">
-        <v>54.6</v>
-      </c>
-      <c r="G6">
-        <v>98</v>
-      </c>
-      <c r="H6">
-        <v>65.40000000000001</v>
+      <c r="C8">
+        <v>4416</v>
+      </c>
+      <c r="D8">
+        <v>220.8</v>
+      </c>
+      <c r="E8">
+        <v>4342</v>
+      </c>
+      <c r="F8">
+        <v>27.6</v>
+      </c>
+      <c r="G8">
+        <v>75</v>
+      </c>
+      <c r="H8">
+        <v>34.2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" t="s">
+        <v>13</v>
+      </c>
+      <c r="B9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C9">
+        <v>20546</v>
+      </c>
+      <c r="D9">
+        <v>1027.3</v>
+      </c>
+      <c r="E9">
+        <v>17307</v>
+      </c>
+      <c r="F9">
+        <v>202.8</v>
+      </c>
+      <c r="G9">
+        <v>364</v>
+      </c>
+      <c r="H9">
+        <v>87.2</v>
       </c>
     </row>
   </sheetData>
@@ -706,62 +813,77 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" s="1" t="s">
+      <c r="B2">
+        <v>25</v>
+      </c>
+      <c r="C2">
+        <v>26</v>
+      </c>
+      <c r="D2">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B2">
-        <v>10</v>
-      </c>
-      <c r="C2">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" s="1" t="s">
-        <v>20</v>
-      </c>
       <c r="B3">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
+        <v>6</v>
+      </c>
+      <c r="D3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
         <v>23</v>
       </c>
       <c r="B4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C4">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:3">
+      <c r="D4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B5">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="C5">
-        <v>10</v>
+        <v>32</v>
+      </c>
+      <c r="D5">
+        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -776,58 +898,58 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D2">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C3">
         <v>2</v>
       </c>
       <c r="D3">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B4">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D4">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>

--- a/sum_daily_order/result/Weekly_Performance_Report_JP_local.xlsx
+++ b/sum_daily_order/result/Weekly_Performance_Report_JP_local.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="29">
   <si>
     <t>文件名称</t>
   </si>
@@ -52,6 +52,9 @@
     <t>0331.csv</t>
   </si>
   <si>
+    <t>0401.csv</t>
+  </si>
+  <si>
     <t>2026-03-29</t>
   </si>
   <si>
@@ -59,6 +62,9 @@
   </si>
   <si>
     <t>2026-03-31</t>
+  </si>
+  <si>
+    <t>2026-04-01</t>
   </si>
   <si>
     <t>日期</t>
@@ -455,7 +461,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -489,7 +495,7 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C2">
         <v>23101</v>
@@ -515,7 +521,7 @@
         <v>9</v>
       </c>
       <c r="B3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C3">
         <v>24379</v>
@@ -541,7 +547,7 @@
         <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C4">
         <v>24962</v>
@@ -560,6 +566,32 @@
       </c>
       <c r="H4">
         <v>121.4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5">
+        <v>18488</v>
+      </c>
+      <c r="D5">
+        <v>924.4</v>
+      </c>
+      <c r="E5">
+        <v>17040</v>
+      </c>
+      <c r="F5">
+        <v>157</v>
+      </c>
+      <c r="G5">
+        <v>311.5</v>
+      </c>
+      <c r="H5">
+        <v>155.6</v>
       </c>
     </row>
   </sheetData>
@@ -569,41 +601,41 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C2">
         <v>4680</v>
@@ -626,10 +658,10 @@
     </row>
     <row r="3" spans="1:8">
       <c r="A3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C3">
         <v>17733</v>
@@ -652,10 +684,10 @@
     </row>
     <row r="4" spans="1:8">
       <c r="A4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B4" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C4">
         <v>688</v>
@@ -678,10 +710,10 @@
     </row>
     <row r="5" spans="1:8">
       <c r="A5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B5" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C5">
         <v>4416</v>
@@ -704,10 +736,10 @@
     </row>
     <row r="6" spans="1:8">
       <c r="A6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B6" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C6">
         <v>19275</v>
@@ -730,10 +762,10 @@
     </row>
     <row r="7" spans="1:8">
       <c r="A7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B7" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C7">
         <v>688</v>
@@ -756,10 +788,10 @@
     </row>
     <row r="8" spans="1:8">
       <c r="A8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C8">
         <v>4416</v>
@@ -782,10 +814,10 @@
     </row>
     <row r="9" spans="1:8">
       <c r="A9" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C9">
         <v>20546</v>
@@ -803,6 +835,58 @@
         <v>364</v>
       </c>
       <c r="H9">
+        <v>87.2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" t="s">
+        <v>15</v>
+      </c>
+      <c r="B10" t="s">
+        <v>23</v>
+      </c>
+      <c r="C10">
+        <v>5652</v>
+      </c>
+      <c r="D10">
+        <v>282.6</v>
+      </c>
+      <c r="E10">
+        <v>5108</v>
+      </c>
+      <c r="F10">
+        <v>32.2</v>
+      </c>
+      <c r="G10">
+        <v>87.5</v>
+      </c>
+      <c r="H10">
+        <v>68.40000000000001</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="A11" t="s">
+        <v>15</v>
+      </c>
+      <c r="B11" t="s">
+        <v>24</v>
+      </c>
+      <c r="C11">
+        <v>12836</v>
+      </c>
+      <c r="D11">
+        <v>641.8</v>
+      </c>
+      <c r="E11">
+        <v>11932</v>
+      </c>
+      <c r="F11">
+        <v>124.8</v>
+      </c>
+      <c r="G11">
+        <v>224</v>
+      </c>
+      <c r="H11">
         <v>87.2</v>
       </c>
     </row>
@@ -813,12 +897,12 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>12</v>
@@ -827,63 +911,78 @@
         <v>13</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4">
+        <v>14</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
       <c r="A2" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B2">
+        <v>23</v>
+      </c>
+      <c r="C2">
         <v>25</v>
       </c>
-      <c r="C2">
+      <c r="D2">
         <v>26</v>
       </c>
-      <c r="D2">
+      <c r="E2">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="1" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="3" spans="1:4">
-      <c r="A3" s="1" t="s">
-        <v>21</v>
-      </c>
       <c r="B3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C3">
         <v>6</v>
       </c>
       <c r="D3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
+        <v>6</v>
+      </c>
+      <c r="E3">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
       <c r="A4" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B4">
         <v>1</v>
       </c>
       <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="D4">
         <v>0</v>
       </c>
-      <c r="D4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
+      <c r="E4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
       <c r="A5" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B5">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C5">
         <v>32</v>
       </c>
       <c r="D5">
-        <v>29</v>
+        <v>32</v>
+      </c>
+      <c r="E5">
+        <v>23</v>
       </c>
     </row>
   </sheetData>
@@ -893,26 +992,29 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" s="1" t="s">
         <v>24</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4">
-      <c r="A2" s="1" t="s">
-        <v>22</v>
       </c>
       <c r="B2">
         <v>5</v>
@@ -921,12 +1023,15 @@
         <v>4</v>
       </c>
       <c r="D2">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
+        <v>4</v>
+      </c>
+      <c r="E2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
       <c r="A3" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B3">
         <v>1</v>
@@ -935,12 +1040,15 @@
         <v>2</v>
       </c>
       <c r="D3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
+        <v>4</v>
+      </c>
+      <c r="E3">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
       <c r="A4" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B4">
         <v>6</v>
@@ -949,7 +1057,10 @@
         <v>6</v>
       </c>
       <c r="D4">
-        <v>12</v>
+        <v>8</v>
+      </c>
+      <c r="E4">
+        <v>20</v>
       </c>
     </row>
   </sheetData>

--- a/sum_daily_order/result/Weekly_Performance_Report_JP_local.xlsx
+++ b/sum_daily_order/result/Weekly_Performance_Report_JP_local.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="26">
   <si>
     <t>文件名称</t>
   </si>
@@ -43,28 +43,16 @@
     <t>寄样总支出(含物流)</t>
   </si>
   <si>
-    <t>0329.csv</t>
-  </si>
-  <si>
-    <t>0330.csv</t>
-  </si>
-  <si>
-    <t>0331.csv</t>
-  </si>
-  <si>
-    <t>0401.csv</t>
+    <t>0329week.csv</t>
+  </si>
+  <si>
+    <t>0405week.csv</t>
   </si>
   <si>
     <t>2026-03-29</t>
   </si>
   <si>
-    <t>2026-03-30</t>
-  </si>
-  <si>
-    <t>2026-03-31</t>
-  </si>
-  <si>
-    <t>2026-04-01</t>
+    <t>2026-04-05</t>
   </si>
   <si>
     <t>日期</t>
@@ -86,6 +74,9 @@
   </si>
   <si>
     <t>寄样支出</t>
+  </si>
+  <si>
+    <t>头发护理精华</t>
   </si>
   <si>
     <t>电动剃眉刀</t>
@@ -461,7 +452,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -495,25 +486,25 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C2">
-        <v>23101</v>
+        <v>197121</v>
       </c>
       <c r="D2">
-        <v>1155.05</v>
+        <v>9856.049999999999</v>
       </c>
       <c r="E2">
-        <v>21665</v>
+        <v>187603</v>
       </c>
       <c r="F2">
-        <v>207</v>
+        <v>1837</v>
       </c>
       <c r="G2">
-        <v>402</v>
+        <v>3508</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>493.3</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -521,77 +512,25 @@
         <v>9</v>
       </c>
       <c r="B3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C3">
-        <v>24379</v>
+        <v>191206</v>
       </c>
       <c r="D3">
-        <v>1218.95</v>
+        <v>9560.299999999999</v>
       </c>
       <c r="E3">
-        <v>22283</v>
+        <v>175390</v>
       </c>
       <c r="F3">
-        <v>227.2</v>
+        <v>1715.2</v>
       </c>
       <c r="G3">
-        <v>442.5</v>
+        <v>3286.5</v>
       </c>
       <c r="H3">
-        <v>126.1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8">
-      <c r="A4" t="s">
-        <v>10</v>
-      </c>
-      <c r="B4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C4">
-        <v>24962</v>
-      </c>
-      <c r="D4">
-        <v>1248.1</v>
-      </c>
-      <c r="E4">
-        <v>21649</v>
-      </c>
-      <c r="F4">
-        <v>230.4</v>
-      </c>
-      <c r="G4">
-        <v>439</v>
-      </c>
-      <c r="H4">
-        <v>121.4</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8">
-      <c r="A5" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5" t="s">
-        <v>15</v>
-      </c>
-      <c r="C5">
-        <v>18488</v>
-      </c>
-      <c r="D5">
-        <v>924.4</v>
-      </c>
-      <c r="E5">
-        <v>17040</v>
-      </c>
-      <c r="F5">
-        <v>157</v>
-      </c>
-      <c r="G5">
-        <v>311.5</v>
-      </c>
-      <c r="H5">
-        <v>155.6</v>
+        <v>714.3</v>
       </c>
     </row>
   </sheetData>
@@ -601,56 +540,56 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C2">
-        <v>4680</v>
+        <v>1960</v>
       </c>
       <c r="D2">
-        <v>234</v>
+        <v>98</v>
       </c>
       <c r="E2">
-        <v>3606</v>
+        <v>1960</v>
       </c>
       <c r="F2">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="G2">
-        <v>62.5</v>
+        <v>41</v>
       </c>
       <c r="H2">
         <v>0</v>
@@ -658,236 +597,132 @@
     </row>
     <row r="3" spans="1:8">
       <c r="A3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C3">
-        <v>17733</v>
+        <v>23580</v>
       </c>
       <c r="D3">
-        <v>886.65</v>
+        <v>1179</v>
       </c>
       <c r="E3">
-        <v>17371</v>
+        <v>20553</v>
       </c>
       <c r="F3">
-        <v>179.4</v>
+        <v>133.4</v>
       </c>
       <c r="G3">
-        <v>322</v>
+        <v>362.5</v>
       </c>
       <c r="H3">
-        <v>0</v>
+        <v>188.1</v>
       </c>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C4">
-        <v>688</v>
+        <v>166765</v>
       </c>
       <c r="D4">
-        <v>34.4</v>
+        <v>8338.25</v>
       </c>
       <c r="E4">
-        <v>688</v>
+        <v>160314</v>
       </c>
       <c r="F4">
-        <v>4.6</v>
+        <v>1661.4</v>
       </c>
       <c r="G4">
-        <v>17.5</v>
+        <v>2982</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>305.2</v>
       </c>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C5">
-        <v>4416</v>
+        <v>4816</v>
       </c>
       <c r="D5">
-        <v>220.8</v>
+        <v>240.8</v>
       </c>
       <c r="E5">
-        <v>4049</v>
+        <v>4776</v>
       </c>
       <c r="F5">
-        <v>27.6</v>
+        <v>32.2</v>
       </c>
       <c r="G5">
-        <v>75</v>
+        <v>122.5</v>
       </c>
       <c r="H5">
-        <v>17.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C6">
-        <v>19275</v>
+        <v>38771</v>
       </c>
       <c r="D6">
-        <v>963.75</v>
+        <v>1938.55</v>
       </c>
       <c r="E6">
-        <v>17752</v>
+        <v>36611</v>
       </c>
       <c r="F6">
-        <v>195</v>
+        <v>225.4</v>
       </c>
       <c r="G6">
-        <v>350</v>
+        <v>612.5</v>
       </c>
       <c r="H6">
-        <v>109</v>
+        <v>256.5</v>
       </c>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B7" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C7">
-        <v>688</v>
+        <v>152435</v>
       </c>
       <c r="D7">
-        <v>34.4</v>
+        <v>7621.75</v>
       </c>
       <c r="E7">
-        <v>482</v>
+        <v>138779</v>
       </c>
       <c r="F7">
-        <v>4.6</v>
+        <v>1489.8</v>
       </c>
       <c r="G7">
-        <v>17.5</v>
+        <v>2674</v>
       </c>
       <c r="H7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8">
-      <c r="A8" t="s">
-        <v>14</v>
-      </c>
-      <c r="B8" t="s">
-        <v>23</v>
-      </c>
-      <c r="C8">
-        <v>4416</v>
-      </c>
-      <c r="D8">
-        <v>220.8</v>
-      </c>
-      <c r="E8">
-        <v>4342</v>
-      </c>
-      <c r="F8">
-        <v>27.6</v>
-      </c>
-      <c r="G8">
-        <v>75</v>
-      </c>
-      <c r="H8">
-        <v>34.2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8">
-      <c r="A9" t="s">
-        <v>14</v>
-      </c>
-      <c r="B9" t="s">
-        <v>24</v>
-      </c>
-      <c r="C9">
-        <v>20546</v>
-      </c>
-      <c r="D9">
-        <v>1027.3</v>
-      </c>
-      <c r="E9">
-        <v>17307</v>
-      </c>
-      <c r="F9">
-        <v>202.8</v>
-      </c>
-      <c r="G9">
-        <v>364</v>
-      </c>
-      <c r="H9">
-        <v>87.2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8">
-      <c r="A10" t="s">
-        <v>15</v>
-      </c>
-      <c r="B10" t="s">
-        <v>23</v>
-      </c>
-      <c r="C10">
-        <v>5652</v>
-      </c>
-      <c r="D10">
-        <v>282.6</v>
-      </c>
-      <c r="E10">
-        <v>5108</v>
-      </c>
-      <c r="F10">
-        <v>32.2</v>
-      </c>
-      <c r="G10">
-        <v>87.5</v>
-      </c>
-      <c r="H10">
-        <v>68.40000000000001</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8">
-      <c r="A11" t="s">
-        <v>15</v>
-      </c>
-      <c r="B11" t="s">
-        <v>24</v>
-      </c>
-      <c r="C11">
-        <v>12836</v>
-      </c>
-      <c r="D11">
-        <v>641.8</v>
-      </c>
-      <c r="E11">
-        <v>11932</v>
-      </c>
-      <c r="F11">
-        <v>124.8</v>
-      </c>
-      <c r="G11">
-        <v>224</v>
-      </c>
-      <c r="H11">
-        <v>87.2</v>
+        <v>457.8</v>
       </c>
     </row>
   </sheetData>
@@ -897,92 +732,73 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
       <c r="A2" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B2">
+        <v>213</v>
+      </c>
+      <c r="C2">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B3">
+        <v>29</v>
+      </c>
+      <c r="C3">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4">
+        <v>7</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="C5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B2">
-        <v>23</v>
-      </c>
-      <c r="C2">
-        <v>25</v>
-      </c>
-      <c r="D2">
-        <v>26</v>
-      </c>
-      <c r="E2">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B3">
-        <v>5</v>
-      </c>
-      <c r="C3">
-        <v>6</v>
-      </c>
-      <c r="D3">
-        <v>6</v>
-      </c>
-      <c r="E3">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-      <c r="C4">
-        <v>1</v>
-      </c>
-      <c r="D4">
-        <v>0</v>
-      </c>
-      <c r="E4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="A5" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B5">
-        <v>29</v>
-      </c>
-      <c r="C5">
-        <v>32</v>
-      </c>
-      <c r="D5">
-        <v>32</v>
-      </c>
-      <c r="E5">
-        <v>23</v>
+      <c r="B6">
+        <v>250</v>
+      </c>
+      <c r="C6">
+        <v>240</v>
       </c>
     </row>
   </sheetData>
@@ -992,75 +808,63 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B2">
+        <v>14</v>
+      </c>
+      <c r="C2">
+        <v>21</v>
+      </c>
+      <c r="D2">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B3">
+        <v>11</v>
+      </c>
+      <c r="C3">
+        <v>15</v>
+      </c>
+      <c r="D3">
         <v>26</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2" s="1" t="s">
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B2">
-        <v>5</v>
-      </c>
-      <c r="C2">
-        <v>4</v>
-      </c>
-      <c r="D2">
-        <v>4</v>
-      </c>
-      <c r="E2">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B3">
-        <v>1</v>
-      </c>
-      <c r="C3">
-        <v>2</v>
-      </c>
-      <c r="D3">
-        <v>4</v>
-      </c>
-      <c r="E3">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4" s="1" t="s">
-        <v>27</v>
-      </c>
       <c r="B4">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="C4">
-        <v>6</v>
+        <v>36</v>
       </c>
       <c r="D4">
-        <v>8</v>
-      </c>
-      <c r="E4">
-        <v>20</v>
+        <v>61</v>
       </c>
     </row>
   </sheetData>

--- a/sum_daily_order/result/Weekly_Performance_Report_JP_local.xlsx
+++ b/sum_daily_order/result/Weekly_Performance_Report_JP_local.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="26">
   <si>
     <t>文件名称</t>
   </si>
@@ -43,16 +43,22 @@
     <t>寄样总支出(含物流)</t>
   </si>
   <si>
-    <t>0329week.csv</t>
-  </si>
-  <si>
-    <t>0405week.csv</t>
-  </si>
-  <si>
-    <t>2026-03-29</t>
-  </si>
-  <si>
-    <t>2026-04-05</t>
+    <t>0406.csv</t>
+  </si>
+  <si>
+    <t>0407.csv</t>
+  </si>
+  <si>
+    <t>0408.csv</t>
+  </si>
+  <si>
+    <t>2026-04-06</t>
+  </si>
+  <si>
+    <t>2026-04-07</t>
+  </si>
+  <si>
+    <t>2026-04-08</t>
   </si>
   <si>
     <t>日期</t>
@@ -76,16 +82,10 @@
     <t>寄样支出</t>
   </si>
   <si>
-    <t>头发护理精华</t>
-  </si>
-  <si>
     <t>电动剃眉刀</t>
   </si>
   <si>
     <t>电动鼻毛刀</t>
-  </si>
-  <si>
-    <t>车载手机支架</t>
   </si>
   <si>
     <t>产品名称</t>
@@ -452,7 +452,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -486,25 +486,25 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C2">
-        <v>197121</v>
+        <v>19350</v>
       </c>
       <c r="D2">
-        <v>9856.049999999999</v>
+        <v>967.5</v>
       </c>
       <c r="E2">
-        <v>187603</v>
+        <v>17196</v>
       </c>
       <c r="F2">
-        <v>1837</v>
+        <v>154.2</v>
       </c>
       <c r="G2">
-        <v>3508</v>
+        <v>289.5</v>
       </c>
       <c r="H2">
-        <v>493.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -512,25 +512,51 @@
         <v>9</v>
       </c>
       <c r="B3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C3">
-        <v>191206</v>
+        <v>20406</v>
       </c>
       <c r="D3">
-        <v>9560.299999999999</v>
+        <v>1020.3</v>
       </c>
       <c r="E3">
-        <v>175390</v>
+        <v>19161</v>
       </c>
       <c r="F3">
-        <v>1715.2</v>
+        <v>190</v>
       </c>
       <c r="G3">
-        <v>3286.5</v>
+        <v>358</v>
       </c>
       <c r="H3">
-        <v>714.3</v>
+        <v>155.6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4">
+        <v>29373</v>
+      </c>
+      <c r="D4">
+        <v>1468.65</v>
+      </c>
+      <c r="E4">
+        <v>27629</v>
+      </c>
+      <c r="F4">
+        <v>274</v>
+      </c>
+      <c r="G4">
+        <v>521.5</v>
+      </c>
+      <c r="H4">
+        <v>155.6</v>
       </c>
     </row>
   </sheetData>
@@ -545,51 +571,51 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C2">
-        <v>1960</v>
+        <v>2453</v>
       </c>
       <c r="D2">
-        <v>98</v>
+        <v>122.65</v>
       </c>
       <c r="E2">
-        <v>1960</v>
+        <v>2273</v>
       </c>
       <c r="F2">
-        <v>10</v>
+        <v>13.8</v>
       </c>
       <c r="G2">
-        <v>41</v>
+        <v>37.5</v>
       </c>
       <c r="H2">
         <v>0</v>
@@ -597,132 +623,132 @@
     </row>
     <row r="3" spans="1:8">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C3">
-        <v>23580</v>
+        <v>16897</v>
       </c>
       <c r="D3">
-        <v>1179</v>
+        <v>844.85</v>
       </c>
       <c r="E3">
-        <v>20553</v>
+        <v>14923</v>
       </c>
       <c r="F3">
-        <v>133.4</v>
+        <v>140.4</v>
       </c>
       <c r="G3">
-        <v>362.5</v>
+        <v>252</v>
       </c>
       <c r="H3">
-        <v>188.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B4" t="s">
         <v>21</v>
       </c>
       <c r="C4">
-        <v>166765</v>
+        <v>2944</v>
       </c>
       <c r="D4">
-        <v>8338.25</v>
+        <v>147.2</v>
       </c>
       <c r="E4">
-        <v>160314</v>
+        <v>2723</v>
       </c>
       <c r="F4">
-        <v>1661.4</v>
+        <v>18.4</v>
       </c>
       <c r="G4">
-        <v>2982</v>
+        <v>50</v>
       </c>
       <c r="H4">
-        <v>305.2</v>
+        <v>68.40000000000001</v>
       </c>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B5" t="s">
         <v>22</v>
       </c>
       <c r="C5">
-        <v>4816</v>
+        <v>17462</v>
       </c>
       <c r="D5">
-        <v>240.8</v>
+        <v>873.1</v>
       </c>
       <c r="E5">
-        <v>4776</v>
+        <v>16438</v>
       </c>
       <c r="F5">
-        <v>32.2</v>
+        <v>171.6</v>
       </c>
       <c r="G5">
-        <v>122.5</v>
+        <v>308</v>
       </c>
       <c r="H5">
-        <v>0</v>
+        <v>87.2</v>
       </c>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C6">
-        <v>38771</v>
+        <v>5372</v>
       </c>
       <c r="D6">
-        <v>1938.55</v>
+        <v>268.6</v>
       </c>
       <c r="E6">
-        <v>36611</v>
+        <v>4936</v>
       </c>
       <c r="F6">
-        <v>225.4</v>
+        <v>32.2</v>
       </c>
       <c r="G6">
-        <v>612.5</v>
+        <v>87.5</v>
       </c>
       <c r="H6">
-        <v>256.5</v>
+        <v>68.40000000000001</v>
       </c>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C7">
-        <v>152435</v>
+        <v>24001</v>
       </c>
       <c r="D7">
-        <v>7621.75</v>
+        <v>1200.05</v>
       </c>
       <c r="E7">
-        <v>138779</v>
+        <v>22693</v>
       </c>
       <c r="F7">
-        <v>1489.8</v>
+        <v>241.8</v>
       </c>
       <c r="G7">
-        <v>2674</v>
+        <v>434</v>
       </c>
       <c r="H7">
-        <v>457.8</v>
+        <v>87.2</v>
       </c>
     </row>
   </sheetData>
@@ -732,73 +758,63 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
         <v>23</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
+        <v>12</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B2">
+        <v>18</v>
+      </c>
+      <c r="C2">
+        <v>22</v>
+      </c>
+      <c r="D2">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B2">
-        <v>213</v>
-      </c>
-      <c r="C2">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" s="1" t="s">
-        <v>20</v>
-      </c>
       <c r="B3">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="C3">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
+        <v>4</v>
+      </c>
+      <c r="D3">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B4">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="C4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B5">
-        <v>1</v>
-      </c>
-      <c r="C5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B6">
-        <v>250</v>
-      </c>
-      <c r="C6">
-        <v>240</v>
+        <v>26</v>
+      </c>
+      <c r="D4">
+        <v>38</v>
       </c>
     </row>
   </sheetData>
@@ -816,10 +832,10 @@
         <v>23</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>25</v>
@@ -830,27 +846,27 @@
         <v>21</v>
       </c>
       <c r="B2">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="C2">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="D2">
-        <v>35</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B3">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="C3">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="D3">
-        <v>26</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -858,13 +874,13 @@
         <v>24</v>
       </c>
       <c r="B4">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="C4">
-        <v>36</v>
+        <v>8</v>
       </c>
       <c r="D4">
-        <v>61</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>

--- a/sum_daily_order/result/Weekly_Performance_Report_JP_local.xlsx
+++ b/sum_daily_order/result/Weekly_Performance_Report_JP_local.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="25">
   <si>
     <t>文件名称</t>
   </si>
@@ -43,22 +43,16 @@
     <t>寄样总支出(含物流)</t>
   </si>
   <si>
-    <t>0406.csv</t>
-  </si>
-  <si>
-    <t>0407.csv</t>
-  </si>
-  <si>
-    <t>0408.csv</t>
-  </si>
-  <si>
-    <t>2026-04-06</t>
-  </si>
-  <si>
-    <t>2026-04-07</t>
-  </si>
-  <si>
-    <t>2026-04-08</t>
+    <t>0406week.csv</t>
+  </si>
+  <si>
+    <t>0412week.csv</t>
+  </si>
+  <si>
+    <t>2026-04-05</t>
+  </si>
+  <si>
+    <t>2026-04-12</t>
   </si>
   <si>
     <t>日期</t>
@@ -86,6 +80,9 @@
   </si>
   <si>
     <t>电动鼻毛刀</t>
+  </si>
+  <si>
+    <t>头发护理精华</t>
   </si>
   <si>
     <t>产品名称</t>
@@ -101,16 +98,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+  <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -126,7 +115,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -134,30 +123,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -452,32 +423,32 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" t="s">
         <v>7</v>
       </c>
     </row>
@@ -486,25 +457,25 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C2">
-        <v>19350</v>
+        <v>190435</v>
       </c>
       <c r="D2">
-        <v>967.5</v>
+        <v>9521.75</v>
       </c>
       <c r="E2">
-        <v>17196</v>
+        <v>174619</v>
       </c>
       <c r="F2">
-        <v>154.2</v>
+        <v>1707.4</v>
       </c>
       <c r="G2">
-        <v>289.5</v>
+        <v>3272.5</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>714.3</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -512,51 +483,25 @@
         <v>9</v>
       </c>
       <c r="B3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C3">
-        <v>20406</v>
+        <v>189378</v>
       </c>
       <c r="D3">
-        <v>1020.3</v>
+        <v>9468.9</v>
       </c>
       <c r="E3">
-        <v>19161</v>
+        <v>147948</v>
       </c>
       <c r="F3">
-        <v>190</v>
+        <v>1733.2</v>
       </c>
       <c r="G3">
-        <v>358</v>
+        <v>3248.5</v>
       </c>
       <c r="H3">
-        <v>155.6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8">
-      <c r="A4" t="s">
-        <v>10</v>
-      </c>
-      <c r="B4" t="s">
-        <v>13</v>
-      </c>
-      <c r="C4">
-        <v>29373</v>
-      </c>
-      <c r="D4">
-        <v>1468.65</v>
-      </c>
-      <c r="E4">
-        <v>27629</v>
-      </c>
-      <c r="F4">
-        <v>274</v>
-      </c>
-      <c r="G4">
-        <v>521.5</v>
-      </c>
-      <c r="H4">
-        <v>155.6</v>
+        <v>793.9</v>
       </c>
     </row>
   </sheetData>
@@ -566,189 +511,163 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1" t="s">
         <v>14</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
         <v>15</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="F1" t="s">
         <v>16</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
+      <c r="G1" t="s">
         <v>17</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="H1" t="s">
         <v>18</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C2">
-        <v>2453</v>
+        <v>38771</v>
       </c>
       <c r="D2">
-        <v>122.65</v>
+        <v>1938.55</v>
       </c>
       <c r="E2">
-        <v>2273</v>
+        <v>36611</v>
       </c>
       <c r="F2">
-        <v>13.8</v>
+        <v>225.4</v>
       </c>
       <c r="G2">
-        <v>37.5</v>
+        <v>612.5</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>256.5</v>
       </c>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C3">
-        <v>16897</v>
+        <v>151664</v>
       </c>
       <c r="D3">
-        <v>844.85</v>
+        <v>7583.2</v>
       </c>
       <c r="E3">
-        <v>14923</v>
+        <v>138008</v>
       </c>
       <c r="F3">
-        <v>140.4</v>
+        <v>1482</v>
       </c>
       <c r="G3">
-        <v>252</v>
+        <v>2660</v>
       </c>
       <c r="H3">
-        <v>0</v>
+        <v>457.8</v>
       </c>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B4" t="s">
         <v>21</v>
       </c>
       <c r="C4">
-        <v>2944</v>
+        <v>2160</v>
       </c>
       <c r="D4">
-        <v>147.2</v>
+        <v>108</v>
       </c>
       <c r="E4">
-        <v>2723</v>
+        <v>1860</v>
       </c>
       <c r="F4">
-        <v>18.4</v>
+        <v>10</v>
       </c>
       <c r="G4">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="H4">
-        <v>68.40000000000001</v>
+        <v>204</v>
       </c>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C5">
-        <v>17462</v>
+        <v>21417</v>
       </c>
       <c r="D5">
-        <v>873.1</v>
+        <v>1070.85</v>
       </c>
       <c r="E5">
-        <v>16438</v>
+        <v>17680</v>
       </c>
       <c r="F5">
-        <v>171.6</v>
+        <v>124.2</v>
       </c>
       <c r="G5">
-        <v>308</v>
+        <v>337.5</v>
       </c>
       <c r="H5">
-        <v>87.2</v>
+        <v>153.9</v>
       </c>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C6">
-        <v>5372</v>
+        <v>165801</v>
       </c>
       <c r="D6">
-        <v>268.6</v>
+        <v>8290.049999999999</v>
       </c>
       <c r="E6">
-        <v>4936</v>
+        <v>128408</v>
       </c>
       <c r="F6">
-        <v>32.2</v>
+        <v>1599</v>
       </c>
       <c r="G6">
-        <v>87.5</v>
+        <v>2870</v>
       </c>
       <c r="H6">
-        <v>68.40000000000001</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8">
-      <c r="A7" t="s">
-        <v>13</v>
-      </c>
-      <c r="B7" t="s">
-        <v>22</v>
-      </c>
-      <c r="C7">
-        <v>24001</v>
-      </c>
-      <c r="D7">
-        <v>1200.05</v>
-      </c>
-      <c r="E7">
-        <v>22693</v>
-      </c>
-      <c r="F7">
-        <v>241.8</v>
-      </c>
-      <c r="G7">
-        <v>434</v>
-      </c>
-      <c r="H7">
-        <v>87.2</v>
+        <v>436</v>
       </c>
     </row>
   </sheetData>
@@ -758,63 +677,62 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:4">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:3">
+      <c r="A1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B2">
+        <v>190</v>
+      </c>
+      <c r="C2">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B3">
+        <v>49</v>
+      </c>
+      <c r="C3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4">
+        <v>0</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
         <v>23</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4">
-      <c r="A2" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B2">
-        <v>18</v>
-      </c>
-      <c r="C2">
-        <v>22</v>
-      </c>
-      <c r="D2">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
-      <c r="A3" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B3">
-        <v>3</v>
-      </c>
-      <c r="C3">
-        <v>4</v>
-      </c>
-      <c r="D3">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="A4" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B4">
-        <v>21</v>
-      </c>
-      <c r="C4">
-        <v>26</v>
-      </c>
-      <c r="D4">
-        <v>38</v>
+      <c r="B5">
+        <v>239</v>
+      </c>
+      <c r="C5">
+        <v>233</v>
       </c>
     </row>
   </sheetData>
@@ -824,63 +742,77 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B2">
+        <v>21</v>
+      </c>
+      <c r="C2">
+        <v>20</v>
+      </c>
+      <c r="D2">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B3">
+        <v>15</v>
+      </c>
+      <c r="C3">
+        <v>9</v>
+      </c>
+      <c r="D3">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4">
+        <v>0</v>
+      </c>
+      <c r="C4">
+        <v>4</v>
+      </c>
+      <c r="D4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" t="s">
         <v>23</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4">
-      <c r="A2" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B2">
-        <v>4</v>
-      </c>
-      <c r="C2">
-        <v>4</v>
-      </c>
-      <c r="D2">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
-      <c r="A3" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B3">
-        <v>4</v>
-      </c>
-      <c r="C3">
-        <v>4</v>
-      </c>
-      <c r="D3">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="A4" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B4">
-        <v>8</v>
-      </c>
-      <c r="C4">
-        <v>8</v>
-      </c>
-      <c r="D4">
-        <v>16</v>
+      <c r="B5">
+        <v>36</v>
+      </c>
+      <c r="C5">
+        <v>33</v>
+      </c>
+      <c r="D5">
+        <v>69</v>
       </c>
     </row>
   </sheetData>

--- a/sum_daily_order/result/Weekly_Performance_Report_JP_local.xlsx
+++ b/sum_daily_order/result/Weekly_Performance_Report_JP_local.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="27">
   <si>
     <t>文件名称</t>
   </si>
@@ -43,16 +43,16 @@
     <t>寄样总支出(含物流)</t>
   </si>
   <si>
-    <t>0406week.csv</t>
-  </si>
-  <si>
-    <t>0412week.csv</t>
-  </si>
-  <si>
-    <t>2026-04-05</t>
-  </si>
-  <si>
-    <t>2026-04-12</t>
+    <t>0419week.csv</t>
+  </si>
+  <si>
+    <t>0426week.csv</t>
+  </si>
+  <si>
+    <t>2026-04-19</t>
+  </si>
+  <si>
+    <t>2026-04-26</t>
   </si>
   <si>
     <t>日期</t>
@@ -76,13 +76,19 @@
     <t>寄样支出</t>
   </si>
   <si>
+    <t>发饰水银13/14点</t>
+  </si>
+  <si>
+    <t>头发护理精华</t>
+  </si>
+  <si>
     <t>电动剃眉刀</t>
   </si>
   <si>
     <t>电动鼻毛刀</t>
   </si>
   <si>
-    <t>头发护理精华</t>
+    <t>3D 立体ミニチュアシーンステッカー 10 テーマセット 手帳 DIY デコシール 紙製立体パズル風ステッカー ピンセット付き</t>
   </si>
   <si>
     <t>产品名称</t>
@@ -460,22 +466,22 @@
         <v>10</v>
       </c>
       <c r="C2">
-        <v>190435</v>
+        <v>264653</v>
       </c>
       <c r="D2">
-        <v>9521.75</v>
+        <v>13232.65</v>
       </c>
       <c r="E2">
-        <v>174619</v>
+        <v>183900</v>
       </c>
       <c r="F2">
-        <v>1707.4</v>
+        <v>2530.4</v>
       </c>
       <c r="G2">
-        <v>3272.5</v>
+        <v>4571.9</v>
       </c>
       <c r="H2">
-        <v>714.3</v>
+        <v>1383.2</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -486,22 +492,22 @@
         <v>11</v>
       </c>
       <c r="C3">
-        <v>189378</v>
+        <v>232064</v>
       </c>
       <c r="D3">
-        <v>9468.9</v>
+        <v>11603.2</v>
       </c>
       <c r="E3">
-        <v>147948</v>
+        <v>165498</v>
       </c>
       <c r="F3">
-        <v>1733.2</v>
+        <v>2080.2</v>
       </c>
       <c r="G3">
-        <v>3248.5</v>
+        <v>3866.5</v>
       </c>
       <c r="H3">
-        <v>793.9</v>
+        <v>1179.2</v>
       </c>
     </row>
   </sheetData>
@@ -511,7 +517,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -548,22 +554,22 @@
         <v>19</v>
       </c>
       <c r="C2">
-        <v>38771</v>
+        <v>2836</v>
       </c>
       <c r="D2">
-        <v>1938.55</v>
+        <v>141.8</v>
       </c>
       <c r="E2">
-        <v>36611</v>
+        <v>2436</v>
       </c>
       <c r="F2">
-        <v>225.4</v>
+        <v>32.6</v>
       </c>
       <c r="G2">
-        <v>612.5</v>
+        <v>44.4</v>
       </c>
       <c r="H2">
-        <v>256.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -574,74 +580,74 @@
         <v>20</v>
       </c>
       <c r="C3">
-        <v>151664</v>
+        <v>2160</v>
       </c>
       <c r="D3">
-        <v>7583.2</v>
+        <v>108</v>
       </c>
       <c r="E3">
-        <v>138008</v>
+        <v>1960</v>
       </c>
       <c r="F3">
-        <v>1482</v>
+        <v>10</v>
       </c>
       <c r="G3">
-        <v>2660</v>
+        <v>41</v>
       </c>
       <c r="H3">
-        <v>457.8</v>
+        <v>969</v>
       </c>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B4" t="s">
         <v>21</v>
       </c>
       <c r="C4">
-        <v>2160</v>
+        <v>4280</v>
       </c>
       <c r="D4">
-        <v>108</v>
+        <v>214</v>
       </c>
       <c r="E4">
-        <v>1860</v>
+        <v>2880</v>
       </c>
       <c r="F4">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="G4">
-        <v>41</v>
+        <v>62.5</v>
       </c>
       <c r="H4">
-        <v>204</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B5" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C5">
-        <v>21417</v>
+        <v>255377</v>
       </c>
       <c r="D5">
-        <v>1070.85</v>
+        <v>12768.85</v>
       </c>
       <c r="E5">
-        <v>17680</v>
+        <v>176624</v>
       </c>
       <c r="F5">
-        <v>124.2</v>
+        <v>2464.8</v>
       </c>
       <c r="G5">
-        <v>337.5</v>
+        <v>4424</v>
       </c>
       <c r="H5">
-        <v>153.9</v>
+        <v>414.2</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -649,25 +655,103 @@
         <v>11</v>
       </c>
       <c r="B6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C6">
+        <v>7988</v>
+      </c>
+      <c r="D6">
+        <v>399.4</v>
+      </c>
+      <c r="E6">
+        <v>7008</v>
+      </c>
+      <c r="F6">
+        <v>0</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" t="s">
         <v>20</v>
       </c>
-      <c r="C6">
-        <v>165801</v>
-      </c>
-      <c r="D6">
-        <v>8290.049999999999</v>
-      </c>
-      <c r="E6">
-        <v>128408</v>
-      </c>
-      <c r="F6">
-        <v>1599</v>
-      </c>
-      <c r="G6">
-        <v>2870</v>
-      </c>
-      <c r="H6">
-        <v>436</v>
+      <c r="C7">
+        <v>7264</v>
+      </c>
+      <c r="D7">
+        <v>363.2</v>
+      </c>
+      <c r="E7">
+        <v>5024</v>
+      </c>
+      <c r="F7">
+        <v>30</v>
+      </c>
+      <c r="G7">
+        <v>123</v>
+      </c>
+      <c r="H7">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" t="s">
+        <v>21</v>
+      </c>
+      <c r="C8">
+        <v>11940</v>
+      </c>
+      <c r="D8">
+        <v>597</v>
+      </c>
+      <c r="E8">
+        <v>8940</v>
+      </c>
+      <c r="F8">
+        <v>69</v>
+      </c>
+      <c r="G8">
+        <v>187.5</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" t="s">
+        <v>11</v>
+      </c>
+      <c r="B9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C9">
+        <v>204872</v>
+      </c>
+      <c r="D9">
+        <v>10243.6</v>
+      </c>
+      <c r="E9">
+        <v>144526</v>
+      </c>
+      <c r="F9">
+        <v>1981.2</v>
+      </c>
+      <c r="G9">
+        <v>3556</v>
+      </c>
+      <c r="H9">
+        <v>414.2</v>
       </c>
     </row>
   </sheetData>
@@ -677,12 +761,12 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B1" t="s">
         <v>10</v>
@@ -693,46 +777,68 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B2">
-        <v>190</v>
+        <v>316</v>
       </c>
       <c r="C2">
-        <v>205</v>
+        <v>254</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B3">
-        <v>49</v>
+        <v>5</v>
       </c>
       <c r="C3">
-        <v>27</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B4">
+        <v>2</v>
+      </c>
+      <c r="C4">
         <v>0</v>
-      </c>
-      <c r="C4">
-        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" t="s">
+        <v>20</v>
+      </c>
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="C5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
         <v>23</v>
       </c>
-      <c r="B5">
-        <v>239</v>
-      </c>
-      <c r="C5">
-        <v>233</v>
+      <c r="B6">
+        <v>0</v>
+      </c>
+      <c r="C6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>25</v>
+      </c>
+      <c r="B7">
+        <v>324</v>
+      </c>
+      <c r="C7">
+        <v>276</v>
       </c>
     </row>
   </sheetData>
@@ -747,7 +853,7 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B1" t="s">
         <v>10</v>
@@ -756,63 +862,63 @@
         <v>11</v>
       </c>
       <c r="D1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B2">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C2">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D2">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B3">
         <v>19</v>
       </c>
-      <c r="B3">
+      <c r="C3">
         <v>15</v>
       </c>
-      <c r="C3">
-        <v>9</v>
-      </c>
       <c r="D3">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B4">
         <v>0</v>
       </c>
       <c r="C4">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="D4">
-        <v>4</v>
+        <v>22</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B5">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C5">
-        <v>33</v>
+        <v>56</v>
       </c>
       <c r="D5">
-        <v>69</v>
+        <v>94</v>
       </c>
     </row>
   </sheetData>

--- a/sum_daily_order/result/Weekly_Performance_Report_JP_local.xlsx
+++ b/sum_daily_order/result/Weekly_Performance_Report_JP_local.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="33">
   <si>
     <t>文件名称</t>
   </si>
@@ -43,16 +43,22 @@
     <t>寄样总支出(含物流)</t>
   </si>
   <si>
-    <t>0419week.csv</t>
-  </si>
-  <si>
-    <t>0426week.csv</t>
-  </si>
-  <si>
-    <t>2026-04-19</t>
-  </si>
-  <si>
-    <t>2026-04-26</t>
+    <t>JP-local-2月.csv</t>
+  </si>
+  <si>
+    <t>JP-local-3月.csv</t>
+  </si>
+  <si>
+    <t>JP-local-4月.csv</t>
+  </si>
+  <si>
+    <t>2026-02-28</t>
+  </si>
+  <si>
+    <t>2026-03-31</t>
+  </si>
+  <si>
+    <t>2026-04-30</t>
   </si>
   <si>
     <t>日期</t>
@@ -76,19 +82,31 @@
     <t>寄样支出</t>
   </si>
   <si>
+    <t>发饰水银11点</t>
+  </si>
+  <si>
+    <t>头发护理精华</t>
+  </si>
+  <si>
+    <t>电动剃眉刀</t>
+  </si>
+  <si>
+    <t>电动鼻毛刀</t>
+  </si>
+  <si>
+    <t>白色睫毛推</t>
+  </si>
+  <si>
+    <t>脱毛器</t>
+  </si>
+  <si>
+    <t>车载手机支架</t>
+  </si>
+  <si>
     <t>发饰水银13/14点</t>
   </si>
   <si>
-    <t>头发护理精华</t>
-  </si>
-  <si>
-    <t>电动剃眉刀</t>
-  </si>
-  <si>
-    <t>电动鼻毛刀</t>
-  </si>
-  <si>
-    <t>3D 立体ミニチュアシーンステッカー 10 テーマセット 手帳 DIY デコシール 紙製立体パズル風ステッカー ピンセット付き</t>
+    <t>场景贴纸</t>
   </si>
   <si>
     <t>产品名称</t>
@@ -429,7 +447,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -463,25 +481,25 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C2">
-        <v>264653</v>
+        <v>142827</v>
       </c>
       <c r="D2">
-        <v>13232.65</v>
+        <v>7141.35</v>
       </c>
       <c r="E2">
-        <v>183900</v>
+        <v>132097</v>
       </c>
       <c r="F2">
-        <v>2530.4</v>
+        <v>882.8</v>
       </c>
       <c r="G2">
-        <v>4571.9</v>
+        <v>1963.15</v>
       </c>
       <c r="H2">
-        <v>1383.2</v>
+        <v>1305</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -489,25 +507,51 @@
         <v>9</v>
       </c>
       <c r="B3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C3">
-        <v>232064</v>
+        <v>761392</v>
       </c>
       <c r="D3">
-        <v>11603.2</v>
+        <v>38069.6</v>
       </c>
       <c r="E3">
-        <v>165498</v>
+        <v>694930</v>
       </c>
       <c r="F3">
-        <v>2080.2</v>
+        <v>5339</v>
       </c>
       <c r="G3">
-        <v>3866.5</v>
+        <v>12427.15</v>
       </c>
       <c r="H3">
-        <v>1179.2</v>
+        <v>4809.7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4">
+        <v>975159</v>
+      </c>
+      <c r="D4">
+        <v>48757.95</v>
+      </c>
+      <c r="E4">
+        <v>729736</v>
+      </c>
+      <c r="F4">
+        <v>9099</v>
+      </c>
+      <c r="G4">
+        <v>16646.9</v>
+      </c>
+      <c r="H4">
+        <v>4802.1</v>
       </c>
     </row>
   </sheetData>
@@ -517,56 +561,56 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:H19"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D1" t="s">
         <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="H1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C2">
-        <v>2836</v>
+        <v>1400</v>
       </c>
       <c r="D2">
-        <v>141.8</v>
+        <v>70</v>
       </c>
       <c r="E2">
-        <v>2436</v>
+        <v>1400</v>
       </c>
       <c r="F2">
-        <v>32.6</v>
+        <v>16.3</v>
       </c>
       <c r="G2">
-        <v>44.4</v>
+        <v>22.2</v>
       </c>
       <c r="H2">
         <v>0</v>
@@ -574,80 +618,80 @@
     </row>
     <row r="3" spans="1:8">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C3">
-        <v>2160</v>
+        <v>9408</v>
       </c>
       <c r="D3">
-        <v>108</v>
+        <v>470.4</v>
       </c>
       <c r="E3">
-        <v>1960</v>
+        <v>9408</v>
       </c>
       <c r="F3">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="G3">
-        <v>41</v>
+        <v>164</v>
       </c>
       <c r="H3">
-        <v>969</v>
+        <v>306</v>
       </c>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C4">
-        <v>4280</v>
+        <v>12960</v>
       </c>
       <c r="D4">
-        <v>214</v>
+        <v>648</v>
       </c>
       <c r="E4">
-        <v>2880</v>
+        <v>12474</v>
       </c>
       <c r="F4">
-        <v>23</v>
+        <v>50.59999999999999</v>
       </c>
       <c r="G4">
-        <v>62.5</v>
+        <v>137.5</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>410.4</v>
       </c>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C5">
-        <v>255377</v>
+        <v>93737</v>
       </c>
       <c r="D5">
-        <v>12768.85</v>
+        <v>4686.85</v>
       </c>
       <c r="E5">
-        <v>176624</v>
+        <v>83719</v>
       </c>
       <c r="F5">
-        <v>2464.8</v>
+        <v>647.4</v>
       </c>
       <c r="G5">
-        <v>4424</v>
+        <v>1162</v>
       </c>
       <c r="H5">
-        <v>414.2</v>
+        <v>588.6</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -655,22 +699,22 @@
         <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C6">
-        <v>7988</v>
+        <v>980</v>
       </c>
       <c r="D6">
-        <v>399.4</v>
+        <v>49</v>
       </c>
       <c r="E6">
-        <v>7008</v>
+        <v>862</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>8.9</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>22.45</v>
       </c>
       <c r="H6">
         <v>0</v>
@@ -681,25 +725,25 @@
         <v>11</v>
       </c>
       <c r="B7" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="C7">
-        <v>7264</v>
+        <v>0</v>
       </c>
       <c r="D7">
-        <v>363.2</v>
+        <v>0</v>
       </c>
       <c r="E7">
-        <v>5024</v>
+        <v>0</v>
       </c>
       <c r="F7">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="G7">
-        <v>123</v>
+        <v>0</v>
       </c>
       <c r="H7">
-        <v>765</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -707,22 +751,22 @@
         <v>11</v>
       </c>
       <c r="B8" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="C8">
-        <v>11940</v>
+        <v>24342</v>
       </c>
       <c r="D8">
-        <v>597</v>
+        <v>1217.1</v>
       </c>
       <c r="E8">
-        <v>8940</v>
+        <v>24234</v>
       </c>
       <c r="F8">
-        <v>69</v>
+        <v>119.6</v>
       </c>
       <c r="G8">
-        <v>187.5</v>
+        <v>455</v>
       </c>
       <c r="H8">
         <v>0</v>
@@ -730,28 +774,288 @@
     </row>
     <row r="9" spans="1:8">
       <c r="A9" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B9" t="s">
+        <v>21</v>
+      </c>
+      <c r="C9">
+        <v>1900</v>
+      </c>
+      <c r="D9">
+        <v>95</v>
+      </c>
+      <c r="E9">
+        <v>1400</v>
+      </c>
+      <c r="F9">
+        <v>16.3</v>
+      </c>
+      <c r="G9">
+        <v>22.2</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" t="s">
+        <v>12</v>
+      </c>
+      <c r="B10" t="s">
         <v>22</v>
       </c>
-      <c r="C9">
-        <v>204872</v>
-      </c>
-      <c r="D9">
-        <v>10243.6</v>
-      </c>
-      <c r="E9">
-        <v>144526</v>
-      </c>
-      <c r="F9">
-        <v>1981.2</v>
-      </c>
-      <c r="G9">
-        <v>3556</v>
-      </c>
-      <c r="H9">
-        <v>414.2</v>
+      <c r="C10">
+        <v>234388</v>
+      </c>
+      <c r="D10">
+        <v>11719.4</v>
+      </c>
+      <c r="E10">
+        <v>205004</v>
+      </c>
+      <c r="F10">
+        <v>970</v>
+      </c>
+      <c r="G10">
+        <v>3977</v>
+      </c>
+      <c r="H10">
+        <v>2754</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="A11" t="s">
+        <v>12</v>
+      </c>
+      <c r="B11" t="s">
+        <v>23</v>
+      </c>
+      <c r="C11">
+        <v>104268</v>
+      </c>
+      <c r="D11">
+        <v>5213.4</v>
+      </c>
+      <c r="E11">
+        <v>95177</v>
+      </c>
+      <c r="F11">
+        <v>519.8</v>
+      </c>
+      <c r="G11">
+        <v>1412.5</v>
+      </c>
+      <c r="H11">
+        <v>769.5000000000001</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
+      <c r="A12" t="s">
+        <v>12</v>
+      </c>
+      <c r="B12" t="s">
+        <v>24</v>
+      </c>
+      <c r="C12">
+        <v>407526</v>
+      </c>
+      <c r="D12">
+        <v>20376.3</v>
+      </c>
+      <c r="E12">
+        <v>380657</v>
+      </c>
+      <c r="F12">
+        <v>3759.6</v>
+      </c>
+      <c r="G12">
+        <v>6748</v>
+      </c>
+      <c r="H12">
+        <v>1286.2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
+      <c r="A13" t="s">
+        <v>12</v>
+      </c>
+      <c r="B13" t="s">
+        <v>25</v>
+      </c>
+      <c r="C13">
+        <v>980</v>
+      </c>
+      <c r="D13">
+        <v>49</v>
+      </c>
+      <c r="E13">
+        <v>902</v>
+      </c>
+      <c r="F13">
+        <v>8.9</v>
+      </c>
+      <c r="G13">
+        <v>22.45</v>
+      </c>
+      <c r="H13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
+      <c r="A14" t="s">
+        <v>12</v>
+      </c>
+      <c r="B14" t="s">
+        <v>27</v>
+      </c>
+      <c r="C14">
+        <v>12330</v>
+      </c>
+      <c r="D14">
+        <v>616.5</v>
+      </c>
+      <c r="E14">
+        <v>11790</v>
+      </c>
+      <c r="F14">
+        <v>64.39999999999999</v>
+      </c>
+      <c r="G14">
+        <v>245</v>
+      </c>
+      <c r="H14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8">
+      <c r="A15" t="s">
+        <v>13</v>
+      </c>
+      <c r="B15" t="s">
+        <v>28</v>
+      </c>
+      <c r="C15">
+        <v>2836</v>
+      </c>
+      <c r="D15">
+        <v>141.8</v>
+      </c>
+      <c r="E15">
+        <v>2436</v>
+      </c>
+      <c r="F15">
+        <v>32.6</v>
+      </c>
+      <c r="G15">
+        <v>44.4</v>
+      </c>
+      <c r="H15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8">
+      <c r="A16" t="s">
+        <v>13</v>
+      </c>
+      <c r="B16" t="s">
+        <v>29</v>
+      </c>
+      <c r="C16">
+        <v>16176</v>
+      </c>
+      <c r="D16">
+        <v>808.8</v>
+      </c>
+      <c r="E16">
+        <v>13976</v>
+      </c>
+      <c r="F16">
+        <v>151.2</v>
+      </c>
+      <c r="G16">
+        <v>171</v>
+      </c>
+      <c r="H16">
+        <v>1074</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8">
+      <c r="A17" t="s">
+        <v>13</v>
+      </c>
+      <c r="B17" t="s">
+        <v>22</v>
+      </c>
+      <c r="C17">
+        <v>6480</v>
+      </c>
+      <c r="D17">
+        <v>324</v>
+      </c>
+      <c r="E17">
+        <v>5780</v>
+      </c>
+      <c r="F17">
+        <v>30</v>
+      </c>
+      <c r="G17">
+        <v>123</v>
+      </c>
+      <c r="H17">
+        <v>1734</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8">
+      <c r="A18" t="s">
+        <v>13</v>
+      </c>
+      <c r="B18" t="s">
+        <v>23</v>
+      </c>
+      <c r="C18">
+        <v>68372</v>
+      </c>
+      <c r="D18">
+        <v>3418.6</v>
+      </c>
+      <c r="E18">
+        <v>58316</v>
+      </c>
+      <c r="F18">
+        <v>390.9999999999999</v>
+      </c>
+      <c r="G18">
+        <v>1062.5</v>
+      </c>
+      <c r="H18">
+        <v>359.1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8">
+      <c r="A19" t="s">
+        <v>13</v>
+      </c>
+      <c r="B19" t="s">
+        <v>24</v>
+      </c>
+      <c r="C19">
+        <v>881295</v>
+      </c>
+      <c r="D19">
+        <v>44064.75</v>
+      </c>
+      <c r="E19">
+        <v>649228</v>
+      </c>
+      <c r="F19">
+        <v>8494.199999999999</v>
+      </c>
+      <c r="G19">
+        <v>15246</v>
+      </c>
+      <c r="H19">
+        <v>1635</v>
       </c>
     </row>
   </sheetData>
@@ -761,84 +1065,147 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:4">
       <c r="A1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" t="s">
         <v>24</v>
       </c>
-      <c r="B1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C1" t="s">
+      <c r="B2">
+        <v>83</v>
+      </c>
+      <c r="C2">
+        <v>482</v>
+      </c>
+      <c r="D2">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B3">
         <v>11</v>
       </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" t="s">
+      <c r="C3">
+        <v>113</v>
+      </c>
+      <c r="D3">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B4">
+        <v>0</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+      <c r="D4">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" t="s">
         <v>22</v>
       </c>
-      <c r="B2">
-        <v>316</v>
-      </c>
-      <c r="C2">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" t="s">
+      <c r="B5">
+        <v>4</v>
+      </c>
+      <c r="C5">
+        <v>97</v>
+      </c>
+      <c r="D5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" t="s">
+        <v>28</v>
+      </c>
+      <c r="B6">
+        <v>0</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
+      <c r="D6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" t="s">
+        <v>27</v>
+      </c>
+      <c r="B7">
+        <v>26</v>
+      </c>
+      <c r="C7">
+        <v>14</v>
+      </c>
+      <c r="D7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" t="s">
         <v>21</v>
       </c>
-      <c r="B3">
-        <v>5</v>
-      </c>
-      <c r="C3">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B4">
-        <v>2</v>
-      </c>
-      <c r="C4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" t="s">
-        <v>20</v>
-      </c>
-      <c r="B5">
+      <c r="B8">
         <v>1</v>
       </c>
-      <c r="C5">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" t="s">
-        <v>23</v>
-      </c>
-      <c r="B6">
-        <v>0</v>
-      </c>
-      <c r="C6">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" t="s">
+      <c r="C8">
+        <v>1</v>
+      </c>
+      <c r="D8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" t="s">
         <v>25</v>
       </c>
-      <c r="B7">
-        <v>324</v>
-      </c>
-      <c r="C7">
-        <v>276</v>
+      <c r="B9">
+        <v>1</v>
+      </c>
+      <c r="C9">
+        <v>1</v>
+      </c>
+      <c r="D9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" t="s">
+        <v>31</v>
+      </c>
+      <c r="B10">
+        <v>126</v>
+      </c>
+      <c r="C10">
+        <v>708</v>
+      </c>
+      <c r="D10">
+        <v>1188</v>
       </c>
     </row>
   </sheetData>
@@ -848,77 +1215,126 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:5">
       <c r="A1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" t="s">
         <v>24</v>
       </c>
-      <c r="B1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4">
-      <c r="A2" t="s">
+      <c r="B2">
+        <v>27</v>
+      </c>
+      <c r="C2">
+        <v>59</v>
+      </c>
+      <c r="D2">
+        <v>75</v>
+      </c>
+      <c r="E2">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" t="s">
         <v>22</v>
       </c>
-      <c r="B2">
-        <v>19</v>
-      </c>
-      <c r="C2">
-        <v>19</v>
-      </c>
-      <c r="D2">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
-      <c r="A3" t="s">
-        <v>20</v>
-      </c>
       <c r="B3">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="C3">
-        <v>15</v>
+        <v>54</v>
       </c>
       <c r="D3">
         <v>34</v>
       </c>
-    </row>
-    <row r="4" spans="1:4">
+      <c r="E3">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
       <c r="A4" t="s">
         <v>23</v>
       </c>
       <c r="B4">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="C4">
-        <v>22</v>
+        <v>45</v>
       </c>
       <c r="D4">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
+        <v>21</v>
+      </c>
+      <c r="E4">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
       <c r="A5" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="B5">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="C5">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="D5">
-        <v>94</v>
+        <v>30</v>
+      </c>
+      <c r="E5">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" t="s">
+        <v>26</v>
+      </c>
+      <c r="B6">
+        <v>10</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
+      <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="E6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" t="s">
+        <v>31</v>
+      </c>
+      <c r="B7">
+        <v>67</v>
+      </c>
+      <c r="C7">
+        <v>158</v>
+      </c>
+      <c r="D7">
+        <v>160</v>
+      </c>
+      <c r="E7">
+        <v>385</v>
       </c>
     </row>
   </sheetData>

--- a/sum_daily_order/result/Weekly_Performance_Report_JP_local.xlsx
+++ b/sum_daily_order/result/Weekly_Performance_Report_JP_local.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="39">
   <si>
     <t>文件名称</t>
   </si>
@@ -52,6 +52,9 @@
     <t>JP-local-4月.csv</t>
   </si>
   <si>
+    <t>JP-local-5月.csv</t>
+  </si>
+  <si>
     <t>2026-02-28</t>
   </si>
   <si>
@@ -61,6 +64,9 @@
     <t>2026-04-30</t>
   </si>
   <si>
+    <t>2026-05-31</t>
+  </si>
+  <si>
     <t>日期</t>
   </si>
   <si>
@@ -107,6 +113,18 @@
   </si>
   <si>
     <t>场景贴纸</t>
+  </si>
+  <si>
+    <t>220枚保鲜袋</t>
+  </si>
+  <si>
+    <t>捏捏乐</t>
+  </si>
+  <si>
+    <t>自动折叠雨伞</t>
+  </si>
+  <si>
+    <t>蜻蜓两个装</t>
   </si>
   <si>
     <t>产品名称</t>
@@ -447,7 +465,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -481,7 +499,7 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C2">
         <v>142827</v>
@@ -507,7 +525,7 @@
         <v>9</v>
       </c>
       <c r="B3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C3">
         <v>761392</v>
@@ -533,7 +551,7 @@
         <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C4">
         <v>975159</v>
@@ -552,6 +570,32 @@
       </c>
       <c r="H4">
         <v>4802.1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5">
+        <v>611618</v>
+      </c>
+      <c r="D5">
+        <v>30580.9</v>
+      </c>
+      <c r="E5">
+        <v>445172</v>
+      </c>
+      <c r="F5">
+        <v>5567.6</v>
+      </c>
+      <c r="G5">
+        <v>8804.65</v>
+      </c>
+      <c r="H5">
+        <v>2788.26</v>
       </c>
     </row>
   </sheetData>
@@ -561,41 +605,41 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H19"/>
+  <dimension ref="A1:H27"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D1" t="s">
         <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="H1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C2">
         <v>1400</v>
@@ -618,10 +662,10 @@
     </row>
     <row r="3" spans="1:8">
       <c r="A3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C3">
         <v>9408</v>
@@ -644,10 +688,10 @@
     </row>
     <row r="4" spans="1:8">
       <c r="A4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B4" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C4">
         <v>12960</v>
@@ -670,10 +714,10 @@
     </row>
     <row r="5" spans="1:8">
       <c r="A5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B5" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C5">
         <v>93737</v>
@@ -696,10 +740,10 @@
     </row>
     <row r="6" spans="1:8">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B6" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C6">
         <v>980</v>
@@ -722,10 +766,10 @@
     </row>
     <row r="7" spans="1:8">
       <c r="A7" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B7" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C7">
         <v>0</v>
@@ -748,10 +792,10 @@
     </row>
     <row r="8" spans="1:8">
       <c r="A8" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B8" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C8">
         <v>24342</v>
@@ -774,10 +818,10 @@
     </row>
     <row r="9" spans="1:8">
       <c r="A9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B9" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C9">
         <v>1900</v>
@@ -800,10 +844,10 @@
     </row>
     <row r="10" spans="1:8">
       <c r="A10" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B10" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C10">
         <v>234388</v>
@@ -826,10 +870,10 @@
     </row>
     <row r="11" spans="1:8">
       <c r="A11" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B11" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C11">
         <v>104268</v>
@@ -852,10 +896,10 @@
     </row>
     <row r="12" spans="1:8">
       <c r="A12" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B12" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C12">
         <v>407526</v>
@@ -878,10 +922,10 @@
     </row>
     <row r="13" spans="1:8">
       <c r="A13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B13" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C13">
         <v>980</v>
@@ -904,10 +948,10 @@
     </row>
     <row r="14" spans="1:8">
       <c r="A14" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C14">
         <v>12330</v>
@@ -930,10 +974,10 @@
     </row>
     <row r="15" spans="1:8">
       <c r="A15" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C15">
         <v>2836</v>
@@ -956,10 +1000,10 @@
     </row>
     <row r="16" spans="1:8">
       <c r="A16" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C16">
         <v>16176</v>
@@ -982,10 +1026,10 @@
     </row>
     <row r="17" spans="1:8">
       <c r="A17" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C17">
         <v>6480</v>
@@ -1008,10 +1052,10 @@
     </row>
     <row r="18" spans="1:8">
       <c r="A18" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B18" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C18">
         <v>68372</v>
@@ -1034,10 +1078,10 @@
     </row>
     <row r="19" spans="1:8">
       <c r="A19" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B19" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C19">
         <v>881295</v>
@@ -1056,6 +1100,214 @@
       </c>
       <c r="H19">
         <v>1635</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8">
+      <c r="A20" t="s">
+        <v>15</v>
+      </c>
+      <c r="B20" t="s">
+        <v>32</v>
+      </c>
+      <c r="C20">
+        <v>5196</v>
+      </c>
+      <c r="D20">
+        <v>259.8</v>
+      </c>
+      <c r="E20">
+        <v>4396</v>
+      </c>
+      <c r="F20">
+        <v>22.4</v>
+      </c>
+      <c r="G20">
+        <v>182</v>
+      </c>
+      <c r="H20">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8">
+      <c r="A21" t="s">
+        <v>15</v>
+      </c>
+      <c r="B21" t="s">
+        <v>30</v>
+      </c>
+      <c r="C21">
+        <v>3100</v>
+      </c>
+      <c r="D21">
+        <v>155</v>
+      </c>
+      <c r="E21">
+        <v>2025</v>
+      </c>
+      <c r="F21">
+        <v>32.6</v>
+      </c>
+      <c r="G21">
+        <v>44.4</v>
+      </c>
+      <c r="H21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8">
+      <c r="A22" t="s">
+        <v>15</v>
+      </c>
+      <c r="B22" t="s">
+        <v>31</v>
+      </c>
+      <c r="C22">
+        <v>169077</v>
+      </c>
+      <c r="D22">
+        <v>8453.85</v>
+      </c>
+      <c r="E22">
+        <v>134625</v>
+      </c>
+      <c r="F22">
+        <v>2049.6</v>
+      </c>
+      <c r="G22">
+        <v>2318</v>
+      </c>
+      <c r="H22">
+        <v>1396.2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8">
+      <c r="A23" t="s">
+        <v>15</v>
+      </c>
+      <c r="B23" t="s">
+        <v>33</v>
+      </c>
+      <c r="C23">
+        <v>1130</v>
+      </c>
+      <c r="D23">
+        <v>56.5</v>
+      </c>
+      <c r="E23">
+        <v>930</v>
+      </c>
+      <c r="F23">
+        <v>0</v>
+      </c>
+      <c r="G23">
+        <v>0</v>
+      </c>
+      <c r="H23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8">
+      <c r="A24" t="s">
+        <v>15</v>
+      </c>
+      <c r="B24" t="s">
+        <v>26</v>
+      </c>
+      <c r="C24">
+        <v>425657</v>
+      </c>
+      <c r="D24">
+        <v>21282.85</v>
+      </c>
+      <c r="E24">
+        <v>297632</v>
+      </c>
+      <c r="F24">
+        <v>3416.4</v>
+      </c>
+      <c r="G24">
+        <v>6132</v>
+      </c>
+      <c r="H24">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8">
+      <c r="A25" t="s">
+        <v>15</v>
+      </c>
+      <c r="B25" t="s">
+        <v>27</v>
+      </c>
+      <c r="C25">
+        <v>4720</v>
+      </c>
+      <c r="D25">
+        <v>236</v>
+      </c>
+      <c r="E25">
+        <v>3724</v>
+      </c>
+      <c r="F25">
+        <v>35.6</v>
+      </c>
+      <c r="G25">
+        <v>89.8</v>
+      </c>
+      <c r="H25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8">
+      <c r="A26" t="s">
+        <v>15</v>
+      </c>
+      <c r="B26" t="s">
+        <v>34</v>
+      </c>
+      <c r="C26">
+        <v>1548</v>
+      </c>
+      <c r="D26">
+        <v>77.40000000000001</v>
+      </c>
+      <c r="E26">
+        <v>850</v>
+      </c>
+      <c r="F26">
+        <v>11</v>
+      </c>
+      <c r="G26">
+        <v>38.45</v>
+      </c>
+      <c r="H26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8">
+      <c r="A27" t="s">
+        <v>15</v>
+      </c>
+      <c r="B27" t="s">
+        <v>35</v>
+      </c>
+      <c r="C27">
+        <v>1190</v>
+      </c>
+      <c r="D27">
+        <v>59.5</v>
+      </c>
+      <c r="E27">
+        <v>990</v>
+      </c>
+      <c r="F27">
+        <v>0</v>
+      </c>
+      <c r="G27">
+        <v>0</v>
+      </c>
+      <c r="H27">
+        <v>445.06</v>
       </c>
     </row>
   </sheetData>
@@ -1065,26 +1317,29 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:5">
       <c r="A1" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="B1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4">
+        <v>14</v>
+      </c>
+      <c r="E1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
       <c r="A2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B2">
         <v>83</v>
@@ -1095,10 +1350,13 @@
       <c r="D2">
         <v>1089</v>
       </c>
-    </row>
-    <row r="3" spans="1:4">
+      <c r="E2">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B3">
         <v>11</v>
@@ -1109,10 +1367,13 @@
       <c r="D3">
         <v>85</v>
       </c>
-    </row>
-    <row r="4" spans="1:4">
+      <c r="E3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
       <c r="A4" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -1123,10 +1384,13 @@
       <c r="D4">
         <v>9</v>
       </c>
-    </row>
-    <row r="5" spans="1:4">
+      <c r="E4">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
       <c r="A5" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B5">
         <v>4</v>
@@ -1137,10 +1401,13 @@
       <c r="D5">
         <v>3</v>
       </c>
-    </row>
-    <row r="6" spans="1:4">
+      <c r="E5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
       <c r="A6" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -1151,24 +1418,30 @@
       <c r="D6">
         <v>2</v>
       </c>
-    </row>
-    <row r="7" spans="1:4">
+      <c r="E6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
       <c r="A7" t="s">
+        <v>32</v>
+      </c>
+      <c r="B7">
+        <v>0</v>
+      </c>
+      <c r="C7">
+        <v>0</v>
+      </c>
+      <c r="D7">
+        <v>0</v>
+      </c>
+      <c r="E7">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" t="s">
         <v>27</v>
-      </c>
-      <c r="B7">
-        <v>26</v>
-      </c>
-      <c r="C7">
-        <v>14</v>
-      </c>
-      <c r="D7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4">
-      <c r="A8" t="s">
-        <v>21</v>
       </c>
       <c r="B8">
         <v>1</v>
@@ -1179,33 +1452,110 @@
       <c r="D8">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:4">
+      <c r="E8">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
       <c r="A9" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="B9">
+        <v>0</v>
+      </c>
+      <c r="C9">
+        <v>0</v>
+      </c>
+      <c r="D9">
+        <v>0</v>
+      </c>
+      <c r="E9">
         <v>1</v>
       </c>
-      <c r="C9">
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" t="s">
+        <v>35</v>
+      </c>
+      <c r="B10">
+        <v>0</v>
+      </c>
+      <c r="C10">
+        <v>0</v>
+      </c>
+      <c r="D10">
+        <v>0</v>
+      </c>
+      <c r="E10">
         <v>1</v>
       </c>
-      <c r="D9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4">
-      <c r="A10" t="s">
-        <v>31</v>
-      </c>
-      <c r="B10">
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" t="s">
+        <v>33</v>
+      </c>
+      <c r="B11">
+        <v>0</v>
+      </c>
+      <c r="C11">
+        <v>0</v>
+      </c>
+      <c r="D11">
+        <v>0</v>
+      </c>
+      <c r="E11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" t="s">
+        <v>29</v>
+      </c>
+      <c r="B12">
+        <v>26</v>
+      </c>
+      <c r="C12">
+        <v>14</v>
+      </c>
+      <c r="D12">
+        <v>0</v>
+      </c>
+      <c r="E12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" t="s">
+        <v>23</v>
+      </c>
+      <c r="B13">
+        <v>1</v>
+      </c>
+      <c r="C13">
+        <v>1</v>
+      </c>
+      <c r="D13">
+        <v>0</v>
+      </c>
+      <c r="E13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14" t="s">
+        <v>37</v>
+      </c>
+      <c r="B14">
         <v>126</v>
       </c>
-      <c r="C10">
+      <c r="C14">
         <v>708</v>
       </c>
-      <c r="D10">
+      <c r="D14">
         <v>1188</v>
+      </c>
+      <c r="E14">
+        <v>573</v>
       </c>
     </row>
   </sheetData>
@@ -1215,29 +1565,32 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:6">
       <c r="A1" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="B1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
+        <v>15</v>
+      </c>
+      <c r="F1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
       <c r="A2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B2">
         <v>27</v>
@@ -1249,12 +1602,15 @@
         <v>75</v>
       </c>
       <c r="E2">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
+        <v>20</v>
+      </c>
+      <c r="F2">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
       <c r="A3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B3">
         <v>6</v>
@@ -1266,12 +1622,15 @@
         <v>34</v>
       </c>
       <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3">
         <v>94</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:6">
       <c r="A4" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B4">
         <v>24</v>
@@ -1283,12 +1642,15 @@
         <v>21</v>
       </c>
       <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4">
         <v>90</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:6">
       <c r="A5" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -1300,41 +1662,110 @@
         <v>30</v>
       </c>
       <c r="E5">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
+        <v>39</v>
+      </c>
+      <c r="F5">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
       <c r="A6" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="B6">
+        <v>0</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
+      <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="E6">
+        <v>48</v>
+      </c>
+      <c r="F6">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" t="s">
+        <v>35</v>
+      </c>
+      <c r="B7">
+        <v>0</v>
+      </c>
+      <c r="C7">
+        <v>0</v>
+      </c>
+      <c r="D7">
+        <v>0</v>
+      </c>
+      <c r="E7">
+        <v>17</v>
+      </c>
+      <c r="F7">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" t="s">
+        <v>32</v>
+      </c>
+      <c r="B8">
+        <v>0</v>
+      </c>
+      <c r="C8">
+        <v>0</v>
+      </c>
+      <c r="D8">
+        <v>0</v>
+      </c>
+      <c r="E8">
         <v>10</v>
       </c>
-      <c r="C6">
-        <v>0</v>
-      </c>
-      <c r="D6">
-        <v>0</v>
-      </c>
-      <c r="E6">
+      <c r="F8">
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
-      <c r="A7" t="s">
-        <v>31</v>
-      </c>
-      <c r="B7">
+    <row r="9" spans="1:6">
+      <c r="A9" t="s">
+        <v>28</v>
+      </c>
+      <c r="B9">
+        <v>10</v>
+      </c>
+      <c r="C9">
+        <v>0</v>
+      </c>
+      <c r="D9">
+        <v>0</v>
+      </c>
+      <c r="E9">
+        <v>0</v>
+      </c>
+      <c r="F9">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" t="s">
+        <v>37</v>
+      </c>
+      <c r="B10">
         <v>67</v>
       </c>
-      <c r="C7">
+      <c r="C10">
         <v>158</v>
       </c>
-      <c r="D7">
+      <c r="D10">
         <v>160</v>
       </c>
-      <c r="E7">
-        <v>385</v>
+      <c r="E10">
+        <v>134</v>
+      </c>
+      <c r="F10">
+        <v>519</v>
       </c>
     </row>
   </sheetData>
